--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -787,25 +787,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>645600</v>
+        <v>629300</v>
       </c>
       <c r="E8" s="3">
-        <v>607600</v>
+        <v>592200</v>
       </c>
       <c r="F8" s="3">
-        <v>557600</v>
+        <v>543500</v>
       </c>
       <c r="G8" s="3">
-        <v>623600</v>
+        <v>607800</v>
       </c>
       <c r="H8" s="3">
-        <v>515800</v>
+        <v>502700</v>
       </c>
       <c r="I8" s="3">
-        <v>473800</v>
+        <v>461800</v>
       </c>
       <c r="J8" s="3">
-        <v>425700</v>
+        <v>414900</v>
       </c>
       <c r="K8" s="3">
         <v>641700</v>
@@ -873,25 +873,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>159100</v>
+        <v>155000</v>
       </c>
       <c r="E9" s="3">
-        <v>140900</v>
+        <v>137300</v>
       </c>
       <c r="F9" s="3">
-        <v>148300</v>
+        <v>144600</v>
       </c>
       <c r="G9" s="3">
-        <v>143500</v>
+        <v>139900</v>
       </c>
       <c r="H9" s="3">
-        <v>138000</v>
+        <v>134500</v>
       </c>
       <c r="I9" s="3">
-        <v>128800</v>
+        <v>125500</v>
       </c>
       <c r="J9" s="3">
-        <v>138700</v>
+        <v>135200</v>
       </c>
       <c r="K9" s="3">
         <v>130400</v>
@@ -959,25 +959,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>486600</v>
+        <v>474300</v>
       </c>
       <c r="E10" s="3">
-        <v>466700</v>
+        <v>454900</v>
       </c>
       <c r="F10" s="3">
-        <v>409300</v>
+        <v>398900</v>
       </c>
       <c r="G10" s="3">
-        <v>480100</v>
+        <v>467900</v>
       </c>
       <c r="H10" s="3">
-        <v>377800</v>
+        <v>368200</v>
       </c>
       <c r="I10" s="3">
-        <v>345000</v>
+        <v>336300</v>
       </c>
       <c r="J10" s="3">
-        <v>287000</v>
+        <v>279800</v>
       </c>
       <c r="K10" s="3">
         <v>511300</v>
@@ -1334,26 +1334,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>13900</v>
       </c>
       <c r="E15" s="3">
-        <v>14500</v>
+        <v>14200</v>
       </c>
       <c r="F15" s="3">
-        <v>15000</v>
+        <v>14700</v>
       </c>
       <c r="G15" s="3">
-        <v>13100</v>
+        <v>12800</v>
       </c>
       <c r="H15" s="3">
-        <v>13600</v>
+        <v>13200</v>
       </c>
       <c r="I15" s="3">
-        <v>16400</v>
+        <v>16000</v>
       </c>
       <c r="J15" s="3">
-        <v>12600</v>
+        <v>12300</v>
       </c>
       <c r="K15" s="3">
         <v>2400</v>
@@ -1450,25 +1450,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>324200</v>
+        <v>316000</v>
       </c>
       <c r="E17" s="3">
-        <v>299800</v>
+        <v>292200</v>
       </c>
       <c r="F17" s="3">
-        <v>310700</v>
+        <v>302800</v>
       </c>
       <c r="G17" s="3">
-        <v>316700</v>
+        <v>308700</v>
       </c>
       <c r="H17" s="3">
-        <v>294400</v>
+        <v>287000</v>
       </c>
       <c r="I17" s="3">
-        <v>268200</v>
+        <v>261400</v>
       </c>
       <c r="J17" s="3">
-        <v>273100</v>
+        <v>266200</v>
       </c>
       <c r="K17" s="3">
         <v>248200</v>
@@ -1536,25 +1536,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>321400</v>
+        <v>313300</v>
       </c>
       <c r="E18" s="3">
-        <v>307800</v>
+        <v>300000</v>
       </c>
       <c r="F18" s="3">
-        <v>246900</v>
+        <v>240700</v>
       </c>
       <c r="G18" s="3">
-        <v>306900</v>
+        <v>299100</v>
       </c>
       <c r="H18" s="3">
-        <v>221400</v>
+        <v>215700</v>
       </c>
       <c r="I18" s="3">
-        <v>205600</v>
+        <v>200400</v>
       </c>
       <c r="J18" s="3">
-        <v>152600</v>
+        <v>148700</v>
       </c>
       <c r="K18" s="3">
         <v>393500</v>
@@ -1654,25 +1654,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-217900</v>
+        <v>-194100</v>
       </c>
       <c r="E20" s="3">
-        <v>-203400</v>
+        <v>-198200</v>
       </c>
       <c r="F20" s="3">
-        <v>-161200</v>
+        <v>-157100</v>
       </c>
       <c r="G20" s="3">
-        <v>-249900</v>
+        <v>-243500</v>
       </c>
       <c r="H20" s="3">
-        <v>-139000</v>
+        <v>-135400</v>
       </c>
       <c r="I20" s="3">
-        <v>-266500</v>
+        <v>-259800</v>
       </c>
       <c r="J20" s="3">
-        <v>-177500</v>
+        <v>-173000</v>
       </c>
       <c r="K20" s="3">
         <v>-522600</v>
@@ -1740,25 +1740,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>149400</v>
+        <v>163900</v>
       </c>
       <c r="E21" s="3">
-        <v>150000</v>
+        <v>146200</v>
       </c>
       <c r="F21" s="3">
-        <v>129400</v>
+        <v>126200</v>
       </c>
       <c r="G21" s="3">
-        <v>101200</v>
+        <v>98600</v>
       </c>
       <c r="H21" s="3">
-        <v>124300</v>
+        <v>121200</v>
       </c>
       <c r="I21" s="3">
-        <v>-20500</v>
+        <v>-19900</v>
       </c>
       <c r="J21" s="3">
-        <v>13100</v>
+        <v>12800</v>
       </c>
       <c r="K21" s="3">
         <v>-106600</v>
@@ -1825,26 +1825,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>18300</v>
       </c>
       <c r="E22" s="3">
-        <v>17600</v>
+        <v>17200</v>
       </c>
       <c r="F22" s="3">
-        <v>22700</v>
+        <v>22100</v>
       </c>
       <c r="G22" s="3">
-        <v>28300</v>
+        <v>27600</v>
       </c>
       <c r="H22" s="3">
-        <v>31700</v>
+        <v>30900</v>
       </c>
       <c r="I22" s="3">
-        <v>38500</v>
+        <v>37500</v>
       </c>
       <c r="J22" s="3">
-        <v>34700</v>
+        <v>33800</v>
       </c>
       <c r="K22" s="3">
         <v>34500</v>
@@ -1912,25 +1912,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>103500</v>
+        <v>100900</v>
       </c>
       <c r="E23" s="3">
-        <v>86800</v>
+        <v>84600</v>
       </c>
       <c r="F23" s="3">
-        <v>63100</v>
+        <v>61500</v>
       </c>
       <c r="G23" s="3">
-        <v>28700</v>
+        <v>27900</v>
       </c>
       <c r="H23" s="3">
-        <v>50700</v>
+        <v>49400</v>
       </c>
       <c r="I23" s="3">
-        <v>-99400</v>
+        <v>-96900</v>
       </c>
       <c r="J23" s="3">
-        <v>-59600</v>
+        <v>-58100</v>
       </c>
       <c r="K23" s="3">
         <v>-163600</v>
@@ -1998,25 +1998,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>19000</v>
+        <v>18500</v>
       </c>
       <c r="E24" s="3">
-        <v>23700</v>
+        <v>23100</v>
       </c>
       <c r="F24" s="3">
-        <v>16700</v>
+        <v>16300</v>
       </c>
       <c r="G24" s="3">
-        <v>12500</v>
+        <v>12100</v>
       </c>
       <c r="H24" s="3">
-        <v>10200</v>
+        <v>9900</v>
       </c>
       <c r="I24" s="3">
         <v>1200</v>
       </c>
       <c r="J24" s="3">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="K24" s="3">
         <v>-1800</v>
@@ -2170,25 +2170,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>84600</v>
+        <v>82400</v>
       </c>
       <c r="E26" s="3">
-        <v>63200</v>
+        <v>61600</v>
       </c>
       <c r="F26" s="3">
-        <v>46400</v>
+        <v>45200</v>
       </c>
       <c r="G26" s="3">
-        <v>16200</v>
+        <v>15800</v>
       </c>
       <c r="H26" s="3">
-        <v>40500</v>
+        <v>39500</v>
       </c>
       <c r="I26" s="3">
-        <v>-100600</v>
+        <v>-98100</v>
       </c>
       <c r="J26" s="3">
-        <v>-64400</v>
+        <v>-62700</v>
       </c>
       <c r="K26" s="3">
         <v>-161800</v>
@@ -2256,25 +2256,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>84600</v>
+        <v>81900</v>
       </c>
       <c r="E27" s="3">
-        <v>62800</v>
+        <v>61200</v>
       </c>
       <c r="F27" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="G27" s="3">
-        <v>16200</v>
+        <v>15800</v>
       </c>
       <c r="H27" s="3">
-        <v>41600</v>
+        <v>40600</v>
       </c>
       <c r="I27" s="3">
-        <v>-100200</v>
+        <v>-97700</v>
       </c>
       <c r="J27" s="3">
-        <v>-64400</v>
+        <v>-62800</v>
       </c>
       <c r="K27" s="3">
         <v>-160400</v>
@@ -2686,25 +2686,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>217900</v>
+        <v>194100</v>
       </c>
       <c r="E32" s="3">
-        <v>203400</v>
+        <v>198200</v>
       </c>
       <c r="F32" s="3">
-        <v>161200</v>
+        <v>157100</v>
       </c>
       <c r="G32" s="3">
-        <v>249900</v>
+        <v>243500</v>
       </c>
       <c r="H32" s="3">
-        <v>139000</v>
+        <v>135400</v>
       </c>
       <c r="I32" s="3">
-        <v>266500</v>
+        <v>259800</v>
       </c>
       <c r="J32" s="3">
-        <v>177500</v>
+        <v>173000</v>
       </c>
       <c r="K32" s="3">
         <v>522600</v>
@@ -2772,25 +2772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>84600</v>
+        <v>81900</v>
       </c>
       <c r="E33" s="3">
-        <v>62800</v>
+        <v>61200</v>
       </c>
       <c r="F33" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="G33" s="3">
-        <v>16200</v>
+        <v>15800</v>
       </c>
       <c r="H33" s="3">
-        <v>41600</v>
+        <v>40600</v>
       </c>
       <c r="I33" s="3">
-        <v>-100200</v>
+        <v>-97700</v>
       </c>
       <c r="J33" s="3">
-        <v>-64400</v>
+        <v>-62800</v>
       </c>
       <c r="K33" s="3">
         <v>-160400</v>
@@ -2944,25 +2944,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>84600</v>
+        <v>81900</v>
       </c>
       <c r="E35" s="3">
-        <v>62800</v>
+        <v>61200</v>
       </c>
       <c r="F35" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="G35" s="3">
-        <v>16200</v>
+        <v>15800</v>
       </c>
       <c r="H35" s="3">
-        <v>41600</v>
+        <v>40600</v>
       </c>
       <c r="I35" s="3">
-        <v>-100200</v>
+        <v>-97700</v>
       </c>
       <c r="J35" s="3">
-        <v>-64400</v>
+        <v>-62800</v>
       </c>
       <c r="K35" s="3">
         <v>-160400</v>
@@ -3185,25 +3185,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>759400</v>
+        <v>740200</v>
       </c>
       <c r="E41" s="3">
-        <v>452900</v>
+        <v>441500</v>
       </c>
       <c r="F41" s="3">
-        <v>381600</v>
+        <v>371900</v>
       </c>
       <c r="G41" s="3">
-        <v>311000</v>
+        <v>303200</v>
       </c>
       <c r="H41" s="3">
-        <v>481800</v>
+        <v>469600</v>
       </c>
       <c r="I41" s="3">
-        <v>778700</v>
+        <v>759000</v>
       </c>
       <c r="J41" s="3">
-        <v>857400</v>
+        <v>835700</v>
       </c>
       <c r="K41" s="3">
         <v>907400</v>
@@ -3271,25 +3271,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>420000</v>
+        <v>409400</v>
       </c>
       <c r="E42" s="3">
-        <v>718400</v>
+        <v>700200</v>
       </c>
       <c r="F42" s="3">
-        <v>669800</v>
+        <v>652800</v>
       </c>
       <c r="G42" s="3">
-        <v>710200</v>
+        <v>692200</v>
       </c>
       <c r="H42" s="3">
-        <v>558500</v>
+        <v>544400</v>
       </c>
       <c r="I42" s="3">
-        <v>511600</v>
+        <v>498700</v>
       </c>
       <c r="J42" s="3">
-        <v>519000</v>
+        <v>505900</v>
       </c>
       <c r="K42" s="3">
         <v>402300</v>
@@ -3357,25 +3357,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4463600</v>
+        <v>4350500</v>
       </c>
       <c r="E43" s="3">
-        <v>3940700</v>
+        <v>3840900</v>
       </c>
       <c r="F43" s="3">
-        <v>4018500</v>
+        <v>3916600</v>
       </c>
       <c r="G43" s="3">
-        <v>4386100</v>
+        <v>4275000</v>
       </c>
       <c r="H43" s="3">
-        <v>4000700</v>
+        <v>3899300</v>
       </c>
       <c r="I43" s="3">
-        <v>3777100</v>
+        <v>3681400</v>
       </c>
       <c r="J43" s="3">
-        <v>3963200</v>
+        <v>3862800</v>
       </c>
       <c r="K43" s="3">
         <v>4115000</v>
@@ -3529,25 +3529,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1024100</v>
+        <v>998200</v>
       </c>
       <c r="E45" s="3">
-        <v>931500</v>
+        <v>907900</v>
       </c>
       <c r="F45" s="3">
-        <v>907300</v>
+        <v>884300</v>
       </c>
       <c r="G45" s="3">
-        <v>897100</v>
+        <v>874400</v>
       </c>
       <c r="H45" s="3">
-        <v>716600</v>
+        <v>698400</v>
       </c>
       <c r="I45" s="3">
-        <v>677000</v>
+        <v>659900</v>
       </c>
       <c r="J45" s="3">
-        <v>606500</v>
+        <v>591100</v>
       </c>
       <c r="K45" s="3">
         <v>619300</v>
@@ -3615,25 +3615,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>6667100</v>
+        <v>6498200</v>
       </c>
       <c r="E46" s="3">
-        <v>6043500</v>
+        <v>5890400</v>
       </c>
       <c r="F46" s="3">
-        <v>5977100</v>
+        <v>5825700</v>
       </c>
       <c r="G46" s="3">
-        <v>6304500</v>
+        <v>6144700</v>
       </c>
       <c r="H46" s="3">
-        <v>5757600</v>
+        <v>5611700</v>
       </c>
       <c r="I46" s="3">
-        <v>5744500</v>
+        <v>5598900</v>
       </c>
       <c r="J46" s="3">
-        <v>5946100</v>
+        <v>5795500</v>
       </c>
       <c r="K46" s="3">
         <v>6044000</v>
@@ -3701,25 +3701,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>57800</v>
+        <v>56300</v>
       </c>
       <c r="E47" s="3">
-        <v>52600</v>
+        <v>51300</v>
       </c>
       <c r="F47" s="3">
-        <v>51800</v>
+        <v>50500</v>
       </c>
       <c r="G47" s="3">
-        <v>87600</v>
+        <v>85400</v>
       </c>
       <c r="H47" s="3">
-        <v>101400</v>
+        <v>98800</v>
       </c>
       <c r="I47" s="3">
-        <v>77400</v>
+        <v>75400</v>
       </c>
       <c r="J47" s="3">
-        <v>214500</v>
+        <v>209000</v>
       </c>
       <c r="K47" s="3">
         <v>276400</v>
@@ -3787,25 +3787,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>340500</v>
+        <v>331900</v>
       </c>
       <c r="E48" s="3">
-        <v>349700</v>
+        <v>340800</v>
       </c>
       <c r="F48" s="3">
-        <v>368200</v>
+        <v>358900</v>
       </c>
       <c r="G48" s="3">
-        <v>337500</v>
+        <v>328900</v>
       </c>
       <c r="H48" s="3">
-        <v>337800</v>
+        <v>329300</v>
       </c>
       <c r="I48" s="3">
-        <v>345600</v>
+        <v>336800</v>
       </c>
       <c r="J48" s="3">
-        <v>337600</v>
+        <v>329100</v>
       </c>
       <c r="K48" s="3">
         <v>316800</v>
@@ -3873,25 +3873,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1795700</v>
+        <v>1750200</v>
       </c>
       <c r="E49" s="3">
-        <v>1788400</v>
+        <v>1743100</v>
       </c>
       <c r="F49" s="3">
-        <v>1774100</v>
+        <v>1729100</v>
       </c>
       <c r="G49" s="3">
-        <v>1775100</v>
+        <v>1730100</v>
       </c>
       <c r="H49" s="3">
-        <v>1768200</v>
+        <v>1723400</v>
       </c>
       <c r="I49" s="3">
-        <v>1765800</v>
+        <v>1721100</v>
       </c>
       <c r="J49" s="3">
-        <v>1736800</v>
+        <v>1692800</v>
       </c>
       <c r="K49" s="3">
         <v>1673300</v>
@@ -4131,25 +4131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>152300</v>
+        <v>148400</v>
       </c>
       <c r="E52" s="3">
-        <v>145400</v>
+        <v>141700</v>
       </c>
       <c r="F52" s="3">
-        <v>159100</v>
+        <v>155100</v>
       </c>
       <c r="G52" s="3">
-        <v>182300</v>
+        <v>177700</v>
       </c>
       <c r="H52" s="3">
-        <v>204500</v>
+        <v>199400</v>
       </c>
       <c r="I52" s="3">
-        <v>191700</v>
+        <v>186900</v>
       </c>
       <c r="J52" s="3">
-        <v>165900</v>
+        <v>161700</v>
       </c>
       <c r="K52" s="3">
         <v>189000</v>
@@ -4303,25 +4303,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9013500</v>
+        <v>8785100</v>
       </c>
       <c r="E54" s="3">
-        <v>8379600</v>
+        <v>8167300</v>
       </c>
       <c r="F54" s="3">
-        <v>8330400</v>
+        <v>8119300</v>
       </c>
       <c r="G54" s="3">
-        <v>8686900</v>
+        <v>8466800</v>
       </c>
       <c r="H54" s="3">
-        <v>8169500</v>
+        <v>7962500</v>
       </c>
       <c r="I54" s="3">
-        <v>8125000</v>
+        <v>7919100</v>
       </c>
       <c r="J54" s="3">
-        <v>8400900</v>
+        <v>8188100</v>
       </c>
       <c r="K54" s="3">
         <v>8496900</v>
@@ -4453,25 +4453,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3633800</v>
+        <v>3541700</v>
       </c>
       <c r="E57" s="3">
-        <v>3280500</v>
+        <v>3197400</v>
       </c>
       <c r="F57" s="3">
-        <v>3296400</v>
+        <v>3212800</v>
       </c>
       <c r="G57" s="3">
-        <v>3531700</v>
+        <v>3442200</v>
       </c>
       <c r="H57" s="3">
-        <v>3129700</v>
+        <v>3050400</v>
       </c>
       <c r="I57" s="3">
-        <v>81300</v>
+        <v>79300</v>
       </c>
       <c r="J57" s="3">
-        <v>3155200</v>
+        <v>3075300</v>
       </c>
       <c r="K57" s="3">
         <v>3248800</v>
@@ -4539,25 +4539,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>405000</v>
+        <v>394700</v>
       </c>
       <c r="E58" s="3">
-        <v>392600</v>
+        <v>382700</v>
       </c>
       <c r="F58" s="3">
-        <v>396900</v>
+        <v>386800</v>
       </c>
       <c r="G58" s="3">
-        <v>580400</v>
+        <v>565700</v>
       </c>
       <c r="H58" s="3">
-        <v>514200</v>
+        <v>501200</v>
       </c>
       <c r="I58" s="3">
-        <v>698900</v>
+        <v>681200</v>
       </c>
       <c r="J58" s="3">
-        <v>912800</v>
+        <v>889600</v>
       </c>
       <c r="K58" s="3">
         <v>781800</v>
@@ -4625,25 +4625,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1210500</v>
+        <v>1179900</v>
       </c>
       <c r="E59" s="3">
-        <v>1078400</v>
+        <v>1051100</v>
       </c>
       <c r="F59" s="3">
-        <v>1046300</v>
+        <v>1019800</v>
       </c>
       <c r="G59" s="3">
-        <v>1064500</v>
+        <v>1037500</v>
       </c>
       <c r="H59" s="3">
-        <v>894400</v>
+        <v>871700</v>
       </c>
       <c r="I59" s="3">
-        <v>759300</v>
+        <v>740000</v>
       </c>
       <c r="J59" s="3">
-        <v>719300</v>
+        <v>701100</v>
       </c>
       <c r="K59" s="3">
         <v>569300</v>
@@ -4711,25 +4711,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5249300</v>
+        <v>5116300</v>
       </c>
       <c r="E60" s="3">
-        <v>4751500</v>
+        <v>4631100</v>
       </c>
       <c r="F60" s="3">
-        <v>4739600</v>
+        <v>4619500</v>
       </c>
       <c r="G60" s="3">
-        <v>5176600</v>
+        <v>5045400</v>
       </c>
       <c r="H60" s="3">
-        <v>4538300</v>
+        <v>4423300</v>
       </c>
       <c r="I60" s="3">
-        <v>1539500</v>
+        <v>1500500</v>
       </c>
       <c r="J60" s="3">
-        <v>4787300</v>
+        <v>4666000</v>
       </c>
       <c r="K60" s="3">
         <v>4599900</v>
@@ -4797,25 +4797,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>561200</v>
+        <v>547000</v>
       </c>
       <c r="E61" s="3">
-        <v>519700</v>
+        <v>506600</v>
       </c>
       <c r="F61" s="3">
-        <v>546900</v>
+        <v>533100</v>
       </c>
       <c r="G61" s="3">
-        <v>561100</v>
+        <v>546800</v>
       </c>
       <c r="H61" s="3">
-        <v>710000</v>
+        <v>692000</v>
       </c>
       <c r="I61" s="3">
-        <v>698100</v>
+        <v>680400</v>
       </c>
       <c r="J61" s="3">
-        <v>646500</v>
+        <v>630100</v>
       </c>
       <c r="K61" s="3">
         <v>906000</v>
@@ -4883,25 +4883,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>289500</v>
+        <v>282100</v>
       </c>
       <c r="E62" s="3">
-        <v>280100</v>
+        <v>273000</v>
       </c>
       <c r="F62" s="3">
-        <v>290500</v>
+        <v>283100</v>
       </c>
       <c r="G62" s="3">
-        <v>286400</v>
+        <v>279100</v>
       </c>
       <c r="H62" s="3">
-        <v>296900</v>
+        <v>289400</v>
       </c>
       <c r="I62" s="3">
-        <v>3285000</v>
+        <v>3201800</v>
       </c>
       <c r="J62" s="3">
-        <v>215200</v>
+        <v>209800</v>
       </c>
       <c r="K62" s="3">
         <v>240400</v>
@@ -5227,25 +5227,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6111300</v>
+        <v>5956500</v>
       </c>
       <c r="E66" s="3">
-        <v>5562900</v>
+        <v>5421900</v>
       </c>
       <c r="F66" s="3">
-        <v>5588400</v>
+        <v>5446800</v>
       </c>
       <c r="G66" s="3">
-        <v>6035600</v>
+        <v>5882600</v>
       </c>
       <c r="H66" s="3">
-        <v>5561600</v>
+        <v>5420700</v>
       </c>
       <c r="I66" s="3">
-        <v>5540200</v>
+        <v>5399800</v>
       </c>
       <c r="J66" s="3">
-        <v>5672500</v>
+        <v>5528800</v>
       </c>
       <c r="K66" s="3">
         <v>5764700</v>
@@ -5689,25 +5689,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2971000</v>
+        <v>2895700</v>
       </c>
       <c r="E72" s="3">
-        <v>2878300</v>
+        <v>2805400</v>
       </c>
       <c r="F72" s="3">
-        <v>2811700</v>
+        <v>2740400</v>
       </c>
       <c r="G72" s="3">
-        <v>2754500</v>
+        <v>2684700</v>
       </c>
       <c r="H72" s="3">
-        <v>2705500</v>
+        <v>2637000</v>
       </c>
       <c r="I72" s="3">
-        <v>2682100</v>
+        <v>2614100</v>
       </c>
       <c r="J72" s="3">
-        <v>2803500</v>
+        <v>2732500</v>
       </c>
       <c r="K72" s="3">
         <v>2954400</v>
@@ -6033,25 +6033,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2902100</v>
+        <v>2828600</v>
       </c>
       <c r="E76" s="3">
-        <v>2816700</v>
+        <v>2745300</v>
       </c>
       <c r="F76" s="3">
-        <v>2741900</v>
+        <v>2672400</v>
       </c>
       <c r="G76" s="3">
-        <v>2651400</v>
+        <v>2584200</v>
       </c>
       <c r="H76" s="3">
-        <v>2608000</v>
+        <v>2541900</v>
       </c>
       <c r="I76" s="3">
-        <v>2584800</v>
+        <v>2519300</v>
       </c>
       <c r="J76" s="3">
-        <v>2728500</v>
+        <v>2659300</v>
       </c>
       <c r="K76" s="3">
         <v>2732200</v>
@@ -6296,25 +6296,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>84600</v>
+        <v>81900</v>
       </c>
       <c r="E81" s="3">
-        <v>62800</v>
+        <v>61200</v>
       </c>
       <c r="F81" s="3">
-        <v>46600</v>
+        <v>45400</v>
       </c>
       <c r="G81" s="3">
-        <v>16200</v>
+        <v>15800</v>
       </c>
       <c r="H81" s="3">
-        <v>41600</v>
+        <v>40600</v>
       </c>
       <c r="I81" s="3">
-        <v>-100200</v>
+        <v>-97700</v>
       </c>
       <c r="J81" s="3">
-        <v>-64400</v>
+        <v>-62800</v>
       </c>
       <c r="K81" s="3">
         <v>-160400</v>
@@ -6414,25 +6414,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>45800</v>
+        <v>44700</v>
       </c>
       <c r="E83" s="3">
-        <v>45600</v>
+        <v>44400</v>
       </c>
       <c r="F83" s="3">
-        <v>43700</v>
+        <v>42600</v>
       </c>
       <c r="G83" s="3">
-        <v>44200</v>
+        <v>43000</v>
       </c>
       <c r="H83" s="3">
-        <v>41900</v>
+        <v>40900</v>
       </c>
       <c r="I83" s="3">
-        <v>40500</v>
+        <v>39500</v>
       </c>
       <c r="J83" s="3">
-        <v>38000</v>
+        <v>37100</v>
       </c>
       <c r="K83" s="3">
         <v>22500</v>
@@ -6930,25 +6930,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>13100</v>
+        <v>12700</v>
       </c>
       <c r="E89" s="3">
-        <v>171200</v>
+        <v>166900</v>
       </c>
       <c r="F89" s="3">
-        <v>240300</v>
+        <v>234200</v>
       </c>
       <c r="G89" s="3">
-        <v>70500</v>
+        <v>68800</v>
       </c>
       <c r="H89" s="3">
-        <v>-34800</v>
+        <v>-33900</v>
       </c>
       <c r="I89" s="3">
-        <v>146900</v>
+        <v>143200</v>
       </c>
       <c r="J89" s="3">
-        <v>163500</v>
+        <v>159400</v>
       </c>
       <c r="K89" s="3">
         <v>120100</v>
@@ -7306,25 +7306,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>270700</v>
+        <v>263800</v>
       </c>
       <c r="E94" s="3">
-        <v>-104500</v>
+        <v>-101800</v>
       </c>
       <c r="F94" s="3">
-        <v>10600</v>
+        <v>10300</v>
       </c>
       <c r="G94" s="3">
-        <v>-171300</v>
+        <v>-167000</v>
       </c>
       <c r="H94" s="3">
-        <v>-56900</v>
+        <v>-55500</v>
       </c>
       <c r="I94" s="3">
         <v>-2100</v>
       </c>
       <c r="J94" s="3">
-        <v>-154400</v>
+        <v>-150500</v>
       </c>
       <c r="K94" s="3">
         <v>-51200</v>
@@ -7768,25 +7768,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>22800</v>
+        <v>22200</v>
       </c>
       <c r="E100" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="F100" s="3">
-        <v>-182500</v>
+        <v>-177800</v>
       </c>
       <c r="G100" s="3">
-        <v>-72200</v>
+        <v>-70400</v>
       </c>
       <c r="H100" s="3">
-        <v>-204000</v>
+        <v>-198800</v>
       </c>
       <c r="I100" s="3">
-        <v>-228500</v>
+        <v>-222700</v>
       </c>
       <c r="J100" s="3">
-        <v>-73200</v>
+        <v>-71400</v>
       </c>
       <c r="K100" s="3">
         <v>225100</v>
@@ -7863,16 +7863,16 @@
         <v>2100</v>
       </c>
       <c r="G101" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="H101" s="3">
         <v>-1200</v>
       </c>
       <c r="I101" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="J101" s="3">
-        <v>-2900</v>
+        <v>-2800</v>
       </c>
       <c r="K101" s="3">
         <v>-600</v>
@@ -7940,25 +7940,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>306500</v>
+        <v>298700</v>
       </c>
       <c r="E102" s="3">
-        <v>71400</v>
+        <v>69600</v>
       </c>
       <c r="F102" s="3">
-        <v>70500</v>
+        <v>68700</v>
       </c>
       <c r="G102" s="3">
-        <v>-170800</v>
+        <v>-166500</v>
       </c>
       <c r="H102" s="3">
-        <v>-296900</v>
+        <v>-289300</v>
       </c>
       <c r="I102" s="3">
-        <v>-78700</v>
+        <v>-76700</v>
       </c>
       <c r="J102" s="3">
-        <v>-67000</v>
+        <v>-65300</v>
       </c>
       <c r="K102" s="3">
         <v>293400</v>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,391 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>629300</v>
+        <v>570000</v>
       </c>
       <c r="E8" s="3">
-        <v>592200</v>
+        <v>623700</v>
       </c>
       <c r="F8" s="3">
-        <v>543500</v>
+        <v>580100</v>
       </c>
       <c r="G8" s="3">
-        <v>607800</v>
+        <v>545900</v>
       </c>
       <c r="H8" s="3">
-        <v>502700</v>
+        <v>501000</v>
       </c>
       <c r="I8" s="3">
+        <v>560300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>463500</v>
+      </c>
+      <c r="K8" s="3">
         <v>461800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>414900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>641700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>296000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>118800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>168000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>185000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>182800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>130600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>141300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>144600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>124000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>110000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>100300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>94400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>76600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>18900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>18400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>155000</v>
+        <v>149600</v>
       </c>
       <c r="E9" s="3">
-        <v>137300</v>
+        <v>148300</v>
       </c>
       <c r="F9" s="3">
-        <v>144600</v>
+        <v>142900</v>
       </c>
       <c r="G9" s="3">
-        <v>139900</v>
+        <v>126600</v>
       </c>
       <c r="H9" s="3">
-        <v>134500</v>
+        <v>133300</v>
       </c>
       <c r="I9" s="3">
+        <v>129000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>124000</v>
+      </c>
+      <c r="K9" s="3">
         <v>125500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>135200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>130400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>105900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>58600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>46400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>39900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>40700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>38900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>29500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>23700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>20800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>18900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>16000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>18100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>14900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>16400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>16500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>18800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>13800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>12900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>474300</v>
+        <v>420300</v>
       </c>
       <c r="E10" s="3">
-        <v>454900</v>
+        <v>475400</v>
       </c>
       <c r="F10" s="3">
-        <v>398900</v>
+        <v>437200</v>
       </c>
       <c r="G10" s="3">
-        <v>467900</v>
+        <v>419300</v>
       </c>
       <c r="H10" s="3">
-        <v>368200</v>
+        <v>367800</v>
       </c>
       <c r="I10" s="3">
+        <v>431300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>339400</v>
+      </c>
+      <c r="K10" s="3">
         <v>336300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>279800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>511300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>190100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>60200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>121600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>145100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>142100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>91700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>111700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>120900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>103200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>91100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>84300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>76400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>61700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3">
         <v>5200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>5500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1096,10 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1184,14 @@
       <c r="AD12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1276,14 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,35 +1308,35 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>12800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1329,85 +1368,91 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13900</v>
+        <v>10300</v>
       </c>
       <c r="E15" s="3">
-        <v>14200</v>
+        <v>10800</v>
       </c>
       <c r="F15" s="3">
-        <v>14700</v>
+        <v>12800</v>
       </c>
       <c r="G15" s="3">
-        <v>12800</v>
+        <v>13100</v>
       </c>
       <c r="H15" s="3">
-        <v>13200</v>
+        <v>13500</v>
       </c>
       <c r="I15" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K15" s="3">
         <v>16000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>12300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>27400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>6700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>6200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>4700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>5400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>3700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>3000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>2500</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1415,8 +1460,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1495,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>316000</v>
+        <v>315000</v>
       </c>
       <c r="E17" s="3">
-        <v>292200</v>
+        <v>289300</v>
       </c>
       <c r="F17" s="3">
-        <v>302800</v>
+        <v>291300</v>
       </c>
       <c r="G17" s="3">
-        <v>308700</v>
+        <v>269400</v>
       </c>
       <c r="H17" s="3">
-        <v>287000</v>
+        <v>279100</v>
       </c>
       <c r="I17" s="3">
+        <v>284600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>264600</v>
+      </c>
+      <c r="K17" s="3">
         <v>261400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>266200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>248200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>246300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>137800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>108700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>105800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>97300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>86800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>66800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>57700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>54800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>55900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>42000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>49000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>37000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD17" s="3">
         <v>36000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>28600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>313300</v>
+        <v>255000</v>
       </c>
       <c r="E18" s="3">
-        <v>300000</v>
+        <v>334400</v>
       </c>
       <c r="F18" s="3">
-        <v>240700</v>
+        <v>288800</v>
       </c>
       <c r="G18" s="3">
-        <v>299100</v>
+        <v>276600</v>
       </c>
       <c r="H18" s="3">
-        <v>215700</v>
+        <v>221900</v>
       </c>
       <c r="I18" s="3">
+        <v>275700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>198900</v>
+      </c>
+      <c r="K18" s="3">
         <v>200400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>148700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>393500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>49700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-19000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>59300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>79200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>85600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>43800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>74400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>86900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>69100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>54100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>58300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>45400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>39700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,243 +1713,257 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-194100</v>
+        <v>-139400</v>
       </c>
       <c r="E20" s="3">
-        <v>-198200</v>
+        <v>-178500</v>
       </c>
       <c r="F20" s="3">
-        <v>-157100</v>
+        <v>-178900</v>
       </c>
       <c r="G20" s="3">
-        <v>-243500</v>
+        <v>-182700</v>
       </c>
       <c r="H20" s="3">
-        <v>-135400</v>
+        <v>-144800</v>
       </c>
       <c r="I20" s="3">
+        <v>-224500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-124900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-259800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-173000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-522600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-308900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>146700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-10200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-29500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-19600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-18200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-14800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-12500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-13400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>14400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>10500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>163900</v>
+        <v>155800</v>
       </c>
       <c r="E21" s="3">
-        <v>146200</v>
+        <v>196800</v>
       </c>
       <c r="F21" s="3">
-        <v>126200</v>
+        <v>151100</v>
       </c>
       <c r="G21" s="3">
-        <v>98600</v>
+        <v>134800</v>
       </c>
       <c r="H21" s="3">
-        <v>121200</v>
+        <v>116300</v>
       </c>
       <c r="I21" s="3">
+        <v>90900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>111700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-19900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-106600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-216100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>146500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>66400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>82300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>84700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>43600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>56800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>77600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>59000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>45800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>51400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>37000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>28700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>6900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18300</v>
+        <v>26200</v>
       </c>
       <c r="E22" s="3">
-        <v>17200</v>
+        <v>19600</v>
       </c>
       <c r="F22" s="3">
-        <v>22100</v>
+        <v>16900</v>
       </c>
       <c r="G22" s="3">
-        <v>27600</v>
+        <v>15800</v>
       </c>
       <c r="H22" s="3">
-        <v>30900</v>
+        <v>20400</v>
       </c>
       <c r="I22" s="3">
+        <v>25400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>28500</v>
+      </c>
+      <c r="K22" s="3">
         <v>37500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>33800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>34500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>28400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>14800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>9400</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -1906,180 +1985,198 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>100900</v>
+        <v>89400</v>
       </c>
       <c r="E23" s="3">
-        <v>84600</v>
+        <v>136400</v>
       </c>
       <c r="F23" s="3">
-        <v>61500</v>
+        <v>93000</v>
       </c>
       <c r="G23" s="3">
-        <v>27900</v>
+        <v>78000</v>
       </c>
       <c r="H23" s="3">
-        <v>49400</v>
+        <v>56700</v>
       </c>
       <c r="I23" s="3">
+        <v>25800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-96900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-58100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-163600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-287600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>112800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>40700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>68900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>72700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>31300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>44900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>67000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>50600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>39200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>45800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>32000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>24200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>19900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>10900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>18500</v>
+        <v>20400</v>
       </c>
       <c r="E24" s="3">
-        <v>23100</v>
+        <v>15200</v>
       </c>
       <c r="F24" s="3">
-        <v>16300</v>
+        <v>17000</v>
       </c>
       <c r="G24" s="3">
-        <v>12100</v>
+        <v>21300</v>
       </c>
       <c r="H24" s="3">
-        <v>9900</v>
+        <v>15000</v>
       </c>
       <c r="I24" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-33700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>23900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>7100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>13700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>18200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>15300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>12700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>9300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>7500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>5200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>5200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2261,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>82400</v>
+        <v>69000</v>
       </c>
       <c r="E26" s="3">
-        <v>61600</v>
+        <v>121200</v>
       </c>
       <c r="F26" s="3">
-        <v>45200</v>
+        <v>76000</v>
       </c>
       <c r="G26" s="3">
-        <v>15800</v>
+        <v>56800</v>
       </c>
       <c r="H26" s="3">
-        <v>39500</v>
+        <v>41700</v>
       </c>
       <c r="I26" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>36400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-98100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-62700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-161800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-253800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>101900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>30700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>57300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>48800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>24200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>31300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>48800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>35300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>32200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>33100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>22700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>16700</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>81900</v>
+        <v>68900</v>
       </c>
       <c r="E27" s="3">
-        <v>61200</v>
+        <v>120300</v>
       </c>
       <c r="F27" s="3">
-        <v>45400</v>
+        <v>75500</v>
       </c>
       <c r="G27" s="3">
-        <v>15800</v>
+        <v>56400</v>
       </c>
       <c r="H27" s="3">
-        <v>40600</v>
+        <v>41900</v>
       </c>
       <c r="I27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-97700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-62800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-160400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-252100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>102500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>30700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>58700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>49900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>24800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>31300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>48600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>35300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>32300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>33100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>22700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>16400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2537,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2629,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2721,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2813,198 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>194100</v>
+        <v>139400</v>
       </c>
       <c r="E32" s="3">
-        <v>198200</v>
+        <v>178500</v>
       </c>
       <c r="F32" s="3">
-        <v>157100</v>
+        <v>178900</v>
       </c>
       <c r="G32" s="3">
-        <v>243500</v>
+        <v>182700</v>
       </c>
       <c r="H32" s="3">
-        <v>135400</v>
+        <v>144800</v>
       </c>
       <c r="I32" s="3">
+        <v>224500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>124900</v>
+      </c>
+      <c r="K32" s="3">
         <v>259800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>173000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>522600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>308900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-146700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>10200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>12900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>29500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>19600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>18200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>14800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>12500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>13400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>15400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>81900</v>
+        <v>68900</v>
       </c>
       <c r="E33" s="3">
-        <v>61200</v>
+        <v>120300</v>
       </c>
       <c r="F33" s="3">
-        <v>45400</v>
+        <v>75500</v>
       </c>
       <c r="G33" s="3">
-        <v>15800</v>
+        <v>56400</v>
       </c>
       <c r="H33" s="3">
-        <v>40600</v>
+        <v>41900</v>
       </c>
       <c r="I33" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-97700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-62800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-160400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-252100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>102500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>30700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>58700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>49900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>24800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>31300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>48600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>35300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>32300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>33100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>22700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>16400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3089,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>81900</v>
+        <v>68900</v>
       </c>
       <c r="E35" s="3">
-        <v>61200</v>
+        <v>120300</v>
       </c>
       <c r="F35" s="3">
-        <v>45400</v>
+        <v>75500</v>
       </c>
       <c r="G35" s="3">
-        <v>15800</v>
+        <v>56400</v>
       </c>
       <c r="H35" s="3">
-        <v>40600</v>
+        <v>41900</v>
       </c>
       <c r="I35" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-97700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-62800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-160400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-252100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>102500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>30700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>58700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>49900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>24800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>31300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>48600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>35300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>32300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>33100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>22700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>16400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3316,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,83 +3350,85 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>740200</v>
+        <v>921600</v>
       </c>
       <c r="E41" s="3">
-        <v>441500</v>
+        <v>402100</v>
       </c>
       <c r="F41" s="3">
-        <v>371900</v>
+        <v>682300</v>
       </c>
       <c r="G41" s="3">
-        <v>303200</v>
+        <v>407000</v>
       </c>
       <c r="H41" s="3">
-        <v>469600</v>
+        <v>342800</v>
       </c>
       <c r="I41" s="3">
+        <v>279500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>432900</v>
+      </c>
+      <c r="K41" s="3">
         <v>759000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>835700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>907400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>612600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1137100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>360800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>457800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>429000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>543400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>299300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>178900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>45300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>30100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>16300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>53200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>32100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>33400</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3265,83 +3438,89 @@
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>409400</v>
+        <v>1308800</v>
       </c>
       <c r="E42" s="3">
-        <v>700200</v>
+        <v>1825300</v>
       </c>
       <c r="F42" s="3">
-        <v>652800</v>
+        <v>1223000</v>
       </c>
       <c r="G42" s="3">
-        <v>692200</v>
+        <v>1402800</v>
       </c>
       <c r="H42" s="3">
-        <v>544400</v>
+        <v>1345800</v>
       </c>
       <c r="I42" s="3">
+        <v>1369900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1069800</v>
+      </c>
+      <c r="K42" s="3">
         <v>498700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>505900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>402300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>452300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>968100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1679500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1520700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1601800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>154300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>474300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>542500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>522600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>507400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>497800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>494300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>26300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>48800</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,83 +3530,89 @@
       <c r="AD42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4350500</v>
+        <v>5076800</v>
       </c>
       <c r="E43" s="3">
-        <v>3840900</v>
+        <v>4565700</v>
       </c>
       <c r="F43" s="3">
-        <v>3916600</v>
+        <v>4010600</v>
       </c>
       <c r="G43" s="3">
-        <v>4275000</v>
+        <v>3540800</v>
       </c>
       <c r="H43" s="3">
-        <v>3899300</v>
+        <v>3610600</v>
       </c>
       <c r="I43" s="3">
+        <v>3941000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3594600</v>
+      </c>
+      <c r="K43" s="3">
         <v>3681400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3862800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4115000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4000100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3562700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3331500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3326300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3393000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2683200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2593100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2653500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2338800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2375200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1971100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1667400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1233300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1385400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3437,8 +3622,14 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,83 +3714,89 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>998200</v>
+        <v>71600</v>
       </c>
       <c r="E45" s="3">
-        <v>907900</v>
+        <v>71100</v>
       </c>
       <c r="F45" s="3">
-        <v>884300</v>
+        <v>74600</v>
       </c>
       <c r="G45" s="3">
-        <v>874400</v>
+        <v>79500</v>
       </c>
       <c r="H45" s="3">
-        <v>698400</v>
+        <v>71300</v>
       </c>
       <c r="I45" s="3">
+        <v>74200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>75900</v>
+      </c>
+      <c r="K45" s="3">
         <v>659900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>591100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>619300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>443700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>248600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>206600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>172200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>123600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>82800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>51100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>24500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>28000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>9100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>4100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>8300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>4000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3609,83 +3806,89 @@
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>6498200</v>
+        <v>7378900</v>
       </c>
       <c r="E46" s="3">
-        <v>5890400</v>
+        <v>6864300</v>
       </c>
       <c r="F46" s="3">
-        <v>5825700</v>
+        <v>5990500</v>
       </c>
       <c r="G46" s="3">
-        <v>6144700</v>
+        <v>5430100</v>
       </c>
       <c r="H46" s="3">
-        <v>5611700</v>
+        <v>5370500</v>
       </c>
       <c r="I46" s="3">
+        <v>5664600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>5173200</v>
+      </c>
+      <c r="K46" s="3">
         <v>5598900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5795500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6044000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5508700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5916500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5578400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5477000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5547500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3463800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3417800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3399400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2934700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2921800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2492300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2218900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1300000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1471500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3695,83 +3898,89 @@
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>56300</v>
+        <v>61400</v>
       </c>
       <c r="E47" s="3">
-        <v>51300</v>
+        <v>52100</v>
       </c>
       <c r="F47" s="3">
-        <v>50500</v>
+        <v>51900</v>
       </c>
       <c r="G47" s="3">
-        <v>85400</v>
+        <v>47300</v>
       </c>
       <c r="H47" s="3">
-        <v>98800</v>
+        <v>46600</v>
       </c>
       <c r="I47" s="3">
+        <v>78800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>91100</v>
+      </c>
+      <c r="K47" s="3">
         <v>75400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>209000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>276400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>435900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>694500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>81200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>82600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>12600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>5400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>9700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>5400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>2400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>4000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3781,83 +3990,89 @@
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>331900</v>
+        <v>313800</v>
       </c>
       <c r="E48" s="3">
-        <v>340800</v>
+        <v>307100</v>
       </c>
       <c r="F48" s="3">
-        <v>358900</v>
+        <v>305900</v>
       </c>
       <c r="G48" s="3">
-        <v>328900</v>
+        <v>314200</v>
       </c>
       <c r="H48" s="3">
-        <v>329300</v>
+        <v>330800</v>
       </c>
       <c r="I48" s="3">
+        <v>303200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>303500</v>
+      </c>
+      <c r="K48" s="3">
         <v>336800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>329100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>316800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>262100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>188200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>172800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>134200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>126500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>117700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>117200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>101300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>88500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>70500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>62800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>47500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>46800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>57400</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3867,83 +4082,89 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1750200</v>
+        <v>1624300</v>
       </c>
       <c r="E49" s="3">
-        <v>1743100</v>
+        <v>1624900</v>
       </c>
       <c r="F49" s="3">
-        <v>1729100</v>
+        <v>1613500</v>
       </c>
       <c r="G49" s="3">
-        <v>1730100</v>
+        <v>1606900</v>
       </c>
       <c r="H49" s="3">
-        <v>1723400</v>
+        <v>1594000</v>
       </c>
       <c r="I49" s="3">
+        <v>1594900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1588700</v>
+      </c>
+      <c r="K49" s="3">
         <v>1721100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1692800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1673300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1655300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>220700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>205200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>194600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>151500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>135900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>75200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>69000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>67800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>60700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>58500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>54900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>56800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>55900</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3953,8 +4174,14 @@
       <c r="AD49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4266,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,83 +4358,89 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>148400</v>
+        <v>157600</v>
       </c>
       <c r="E52" s="3">
-        <v>141700</v>
+        <v>148200</v>
       </c>
       <c r="F52" s="3">
-        <v>155100</v>
+        <v>136800</v>
       </c>
       <c r="G52" s="3">
-        <v>177700</v>
+        <v>130600</v>
       </c>
       <c r="H52" s="3">
-        <v>199400</v>
+        <v>143000</v>
       </c>
       <c r="I52" s="3">
+        <v>163800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>183800</v>
+      </c>
+      <c r="K52" s="3">
         <v>186900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>161700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>189000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>135800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>109100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>95100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>51500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>50200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>46400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>49600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>43900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>46600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>51200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>51900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>48400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>46800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>54500</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4211,8 +4450,14 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,83 +4542,89 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8785100</v>
+        <v>9535900</v>
       </c>
       <c r="E54" s="3">
-        <v>8167300</v>
+        <v>8996600</v>
       </c>
       <c r="F54" s="3">
-        <v>8119300</v>
+        <v>8098700</v>
       </c>
       <c r="G54" s="3">
-        <v>8466800</v>
+        <v>7529100</v>
       </c>
       <c r="H54" s="3">
-        <v>7962500</v>
+        <v>7484900</v>
       </c>
       <c r="I54" s="3">
+        <v>7805300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>7340400</v>
+      </c>
+      <c r="K54" s="3">
         <v>7919100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8188100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8496900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7997900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>7129000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6132700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5939900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5888100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3769200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3669500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3621200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3143000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3109300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2667700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2371500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1452700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1643300</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4383,8 +4634,14 @@
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4672,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,83 +4706,85 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3541700</v>
+        <v>3606400</v>
       </c>
       <c r="E57" s="3">
-        <v>3197400</v>
+        <v>3635600</v>
       </c>
       <c r="F57" s="3">
-        <v>3212800</v>
+        <v>3265000</v>
       </c>
       <c r="G57" s="3">
-        <v>3442200</v>
+        <v>2947600</v>
       </c>
       <c r="H57" s="3">
-        <v>3050400</v>
+        <v>2961800</v>
       </c>
       <c r="I57" s="3">
+        <v>3173200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="K57" s="3">
         <v>79300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3075300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3248800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2991400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2156500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1673900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1749800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1691700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1382700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1118700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1218600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1073100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1105200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1088800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>912300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>865300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>940200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4533,83 +4794,89 @@
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>394700</v>
+        <v>412200</v>
       </c>
       <c r="E58" s="3">
-        <v>382700</v>
+        <v>347300</v>
       </c>
       <c r="F58" s="3">
-        <v>386800</v>
+        <v>363900</v>
       </c>
       <c r="G58" s="3">
-        <v>565700</v>
+        <v>352800</v>
       </c>
       <c r="H58" s="3">
-        <v>501200</v>
+        <v>356600</v>
       </c>
       <c r="I58" s="3">
+        <v>521500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>462000</v>
+      </c>
+      <c r="K58" s="3">
         <v>681200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>889600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>781800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>572100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>672500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>656700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>588400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>570000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>739900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>839400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>930600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>512800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>398400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>246700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>138700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>10800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3900</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4619,83 +4886,89 @@
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1179900</v>
+        <v>1391600</v>
       </c>
       <c r="E59" s="3">
-        <v>1051100</v>
+        <v>1401400</v>
       </c>
       <c r="F59" s="3">
-        <v>1019800</v>
+        <v>1087700</v>
       </c>
       <c r="G59" s="3">
-        <v>1037500</v>
+        <v>968900</v>
       </c>
       <c r="H59" s="3">
-        <v>871700</v>
+        <v>940100</v>
       </c>
       <c r="I59" s="3">
+        <v>956400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>803600</v>
+      </c>
+      <c r="K59" s="3">
         <v>740000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>701100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>569300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>422000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>210700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>171300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>165100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>125200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>86200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>57700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>43600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>33500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>35700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>34700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>29100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>46900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>27900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4705,83 +4978,89 @@
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5116300</v>
+        <v>5410200</v>
       </c>
       <c r="E60" s="3">
-        <v>4631100</v>
+        <v>5384400</v>
       </c>
       <c r="F60" s="3">
-        <v>4619500</v>
+        <v>4716500</v>
       </c>
       <c r="G60" s="3">
-        <v>5045400</v>
+        <v>4269300</v>
       </c>
       <c r="H60" s="3">
-        <v>4423300</v>
+        <v>4258600</v>
       </c>
       <c r="I60" s="3">
+        <v>4651200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4077700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1500500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4666000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4599900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3985500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3039800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2502000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2503300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2386800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2208700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2015800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2192900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1619400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1539300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1370300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1080200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>923000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>972100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4791,83 +5070,89 @@
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>547000</v>
+        <v>1118700</v>
       </c>
       <c r="E61" s="3">
-        <v>506600</v>
+        <v>672400</v>
       </c>
       <c r="F61" s="3">
-        <v>533100</v>
+        <v>504200</v>
       </c>
       <c r="G61" s="3">
-        <v>546800</v>
+        <v>467000</v>
       </c>
       <c r="H61" s="3">
-        <v>692000</v>
+        <v>491400</v>
       </c>
       <c r="I61" s="3">
+        <v>504100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>638000</v>
+      </c>
+      <c r="K61" s="3">
         <v>680400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>630100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>906000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>860300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1044200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>560400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>549800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>582500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>241400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>397800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>315400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>462600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>531100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>295800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>367400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>381000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>481100</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -4877,83 +5162,89 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>282100</v>
+        <v>234800</v>
       </c>
       <c r="E62" s="3">
-        <v>273000</v>
+        <v>228300</v>
       </c>
       <c r="F62" s="3">
-        <v>283100</v>
+        <v>260100</v>
       </c>
       <c r="G62" s="3">
-        <v>279100</v>
+        <v>251700</v>
       </c>
       <c r="H62" s="3">
-        <v>289400</v>
+        <v>261000</v>
       </c>
       <c r="I62" s="3">
+        <v>257300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>266800</v>
+      </c>
+      <c r="K62" s="3">
         <v>3201800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>209800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>240400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>227700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>111300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>89400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>81800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>61100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>51000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>9900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>9700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>20200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>19700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>15600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>15400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>18300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>18800</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4963,8 +5254,14 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5346,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5438,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,83 +5530,89 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5956500</v>
+        <v>6773400</v>
       </c>
       <c r="E66" s="3">
-        <v>5421900</v>
+        <v>6295000</v>
       </c>
       <c r="F66" s="3">
-        <v>5446800</v>
+        <v>5491100</v>
       </c>
       <c r="G66" s="3">
-        <v>5882600</v>
+        <v>4998300</v>
       </c>
       <c r="H66" s="3">
-        <v>5420700</v>
+        <v>5021300</v>
       </c>
       <c r="I66" s="3">
+        <v>5423000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>4997100</v>
+      </c>
+      <c r="K66" s="3">
         <v>5399800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5528800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5764700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5090800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4210900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3163600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3160900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3048700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2519400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2442000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2518100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2102100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2090000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1681600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1462900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1325800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1476000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5307,8 +5622,14 @@
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5660,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5748,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5840,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5932,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,83 +6024,89 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2895700</v>
+        <v>2883700</v>
       </c>
       <c r="E72" s="3">
-        <v>2805400</v>
+        <v>2813000</v>
       </c>
       <c r="F72" s="3">
-        <v>2740400</v>
+        <v>2669400</v>
       </c>
       <c r="G72" s="3">
-        <v>2684700</v>
+        <v>2586200</v>
       </c>
       <c r="H72" s="3">
-        <v>2637000</v>
+        <v>2526300</v>
       </c>
       <c r="I72" s="3">
+        <v>2475000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2430900</v>
+      </c>
+      <c r="K72" s="3">
         <v>2614100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2732500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2954400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3096800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3211200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2986400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2794100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2861600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1274000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1250900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1116500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1055200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1034600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>998300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>918700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>132900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>175600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5769,8 +6116,14 @@
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6208,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6300,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,83 +6392,89 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2828600</v>
+        <v>2762500</v>
       </c>
       <c r="E76" s="3">
-        <v>2745300</v>
+        <v>2701600</v>
       </c>
       <c r="F76" s="3">
-        <v>2672400</v>
+        <v>2607600</v>
       </c>
       <c r="G76" s="3">
-        <v>2584200</v>
+        <v>2530800</v>
       </c>
       <c r="H76" s="3">
-        <v>2541900</v>
+        <v>2463600</v>
       </c>
       <c r="I76" s="3">
+        <v>2382300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2343300</v>
+      </c>
+      <c r="K76" s="3">
         <v>2519300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2659300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2732200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2907100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2918100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2969000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2778900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2839400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1249900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1227500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1103100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1040900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1019300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>986200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>908600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>126900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>167300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6113,8 +6484,14 @@
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6576,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>81900</v>
+        <v>68900</v>
       </c>
       <c r="E81" s="3">
-        <v>61200</v>
+        <v>120300</v>
       </c>
       <c r="F81" s="3">
-        <v>45400</v>
+        <v>75500</v>
       </c>
       <c r="G81" s="3">
-        <v>15800</v>
+        <v>56400</v>
       </c>
       <c r="H81" s="3">
-        <v>40600</v>
+        <v>41900</v>
       </c>
       <c r="I81" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-97700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-62800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-160400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-252100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>102500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>30700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>58700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>49900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>24800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>31300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>48600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>35300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>32300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>33100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>22700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>16400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,94 +6803,102 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>44700</v>
+        <v>40200</v>
       </c>
       <c r="E83" s="3">
-        <v>44400</v>
+        <v>40800</v>
       </c>
       <c r="F83" s="3">
-        <v>42600</v>
+        <v>41200</v>
       </c>
       <c r="G83" s="3">
-        <v>43000</v>
+        <v>41000</v>
       </c>
       <c r="H83" s="3">
-        <v>40900</v>
+        <v>39300</v>
       </c>
       <c r="I83" s="3">
+        <v>39700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>37700</v>
+      </c>
+      <c r="K83" s="3">
         <v>39500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>37100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>22500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>43100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>18900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>16400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>12000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>12400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>11900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>10300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>8100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>6400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>5600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>5000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>5300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>4400</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6983,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +7075,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +7167,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7259,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7351,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>12700</v>
+        <v>-456900</v>
       </c>
       <c r="E89" s="3">
-        <v>166900</v>
+        <v>-77000</v>
       </c>
       <c r="F89" s="3">
-        <v>234200</v>
+        <v>11700</v>
       </c>
       <c r="G89" s="3">
-        <v>68800</v>
+        <v>153800</v>
       </c>
       <c r="H89" s="3">
-        <v>-33900</v>
+        <v>215900</v>
       </c>
       <c r="I89" s="3">
+        <v>63400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K89" s="3">
         <v>143200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>159400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>120100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>358300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>256000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>45400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-326800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>219400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>71400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-122500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>35100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-353300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-55200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-379200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>15400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-32200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,94 +7481,102 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-306600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-285300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-176400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-332200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-416400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-155300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-109300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-216800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-241800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-546400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-151300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-36800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-64800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-17800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-17800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-36400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-11700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-10200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7661,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7753,106 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>263800</v>
+        <v>498900</v>
       </c>
       <c r="E94" s="3">
-        <v>-101800</v>
+        <v>-315100</v>
       </c>
       <c r="F94" s="3">
-        <v>10300</v>
+        <v>243200</v>
       </c>
       <c r="G94" s="3">
-        <v>-167000</v>
+        <v>-93900</v>
       </c>
       <c r="H94" s="3">
-        <v>-55500</v>
+        <v>9500</v>
       </c>
       <c r="I94" s="3">
+        <v>-153900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-150500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-51200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-596400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>167200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-121200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-22900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>282300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>97400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-23100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-55100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-19600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>16900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-470400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>4300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>26700</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7883,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7971,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +8063,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +8155,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,262 +8247,286 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>22200</v>
+        <v>477500</v>
       </c>
       <c r="E100" s="3">
-        <v>3100</v>
+        <v>113100</v>
       </c>
       <c r="F100" s="3">
-        <v>-177800</v>
+        <v>20500</v>
       </c>
       <c r="G100" s="3">
-        <v>-70400</v>
+        <v>2900</v>
       </c>
       <c r="H100" s="3">
-        <v>-198800</v>
+        <v>-163900</v>
       </c>
       <c r="I100" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-183300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-222700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-71400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>225100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-328900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>345300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>29800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>21700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1704200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-255100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-60000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>279100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>35200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>387000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>870200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>229100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2100</v>
-      </c>
       <c r="G101" s="3">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="H101" s="3">
-        <v>-1200</v>
+        <v>1900</v>
       </c>
       <c r="I101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K101" s="3">
         <v>4800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>7700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-4300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>298700</v>
+        <v>519500</v>
       </c>
       <c r="E102" s="3">
-        <v>69600</v>
+        <v>-280200</v>
       </c>
       <c r="F102" s="3">
-        <v>68700</v>
+        <v>275400</v>
       </c>
       <c r="G102" s="3">
-        <v>-166500</v>
+        <v>64100</v>
       </c>
       <c r="H102" s="3">
-        <v>-289300</v>
+        <v>63400</v>
       </c>
       <c r="I102" s="3">
+        <v>-153500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-266700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-76700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-65300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>293400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-570100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>776300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-113000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>47600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-114400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>246200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>108400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>133600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>15600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>13800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-39500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>22200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>5700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>125900</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>570000</v>
+        <v>576200</v>
       </c>
       <c r="E8" s="3">
-        <v>623700</v>
+        <v>554400</v>
       </c>
       <c r="F8" s="3">
-        <v>580100</v>
+        <v>606700</v>
       </c>
       <c r="G8" s="3">
-        <v>545900</v>
+        <v>564300</v>
       </c>
       <c r="H8" s="3">
-        <v>501000</v>
+        <v>531100</v>
       </c>
       <c r="I8" s="3">
-        <v>560300</v>
+        <v>487400</v>
       </c>
       <c r="J8" s="3">
+        <v>545000</v>
+      </c>
+      <c r="K8" s="3">
         <v>463500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>461800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>414900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>641700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>296000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>118800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>168000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>185000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>182800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>130600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>141300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>144600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>124000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>110000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>100300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>94400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>76600</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="3">
         <v>18900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>149600</v>
+        <v>151200</v>
       </c>
       <c r="E9" s="3">
-        <v>148300</v>
+        <v>145600</v>
       </c>
       <c r="F9" s="3">
-        <v>142900</v>
+        <v>144300</v>
       </c>
       <c r="G9" s="3">
-        <v>126600</v>
+        <v>139000</v>
       </c>
       <c r="H9" s="3">
-        <v>133300</v>
+        <v>123200</v>
       </c>
       <c r="I9" s="3">
-        <v>129000</v>
+        <v>129600</v>
       </c>
       <c r="J9" s="3">
+        <v>125400</v>
+      </c>
+      <c r="K9" s="3">
         <v>124000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>125500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>135200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>105900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>58600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>46400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>38900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>23700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>420300</v>
+        <v>425000</v>
       </c>
       <c r="E10" s="3">
-        <v>475400</v>
+        <v>408900</v>
       </c>
       <c r="F10" s="3">
-        <v>437200</v>
+        <v>462500</v>
       </c>
       <c r="G10" s="3">
-        <v>419300</v>
+        <v>425300</v>
       </c>
       <c r="H10" s="3">
-        <v>367800</v>
+        <v>407900</v>
       </c>
       <c r="I10" s="3">
-        <v>431300</v>
+        <v>357700</v>
       </c>
       <c r="J10" s="3">
+        <v>419600</v>
+      </c>
+      <c r="K10" s="3">
         <v>339400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>336300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>279800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>511300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>190100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>121600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>145100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>142100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>91700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>111700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>120900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>103200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>91100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>84300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>76400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61700</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="3">
         <v>5200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1314,21 +1334,21 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1374,77 +1394,80 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10300</v>
+        <v>9300</v>
       </c>
       <c r="E15" s="3">
-        <v>10800</v>
+        <v>10000</v>
       </c>
       <c r="F15" s="3">
-        <v>12800</v>
+        <v>10500</v>
       </c>
       <c r="G15" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H15" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I15" s="3">
         <v>13100</v>
       </c>
-      <c r="H15" s="3">
-        <v>13500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>11800</v>
-      </c>
       <c r="J15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K15" s="3">
         <v>12200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
         <v>3700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2500</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1454,8 +1477,8 @@
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>315000</v>
+        <v>306000</v>
       </c>
       <c r="E17" s="3">
-        <v>289300</v>
+        <v>306400</v>
       </c>
       <c r="F17" s="3">
-        <v>291300</v>
+        <v>281400</v>
       </c>
       <c r="G17" s="3">
-        <v>269400</v>
+        <v>283400</v>
       </c>
       <c r="H17" s="3">
-        <v>279100</v>
+        <v>262000</v>
       </c>
       <c r="I17" s="3">
-        <v>284600</v>
+        <v>271500</v>
       </c>
       <c r="J17" s="3">
+        <v>276800</v>
+      </c>
+      <c r="K17" s="3">
         <v>264600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>261400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>266200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>248200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>246300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>137800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>108700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>105800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>97300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>86800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>66800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>57700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>54800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>55900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>42000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>49000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>37000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE17" s="3">
         <v>36000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>28600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>255000</v>
+        <v>270200</v>
       </c>
       <c r="E18" s="3">
-        <v>334400</v>
+        <v>248100</v>
       </c>
       <c r="F18" s="3">
-        <v>288800</v>
+        <v>325300</v>
       </c>
       <c r="G18" s="3">
-        <v>276600</v>
+        <v>280900</v>
       </c>
       <c r="H18" s="3">
-        <v>221900</v>
+        <v>269000</v>
       </c>
       <c r="I18" s="3">
-        <v>275700</v>
+        <v>215800</v>
       </c>
       <c r="J18" s="3">
+        <v>268200</v>
+      </c>
+      <c r="K18" s="3">
         <v>198900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>148700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>393500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>79200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>85600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>74400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>86900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>69100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>54100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>45400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>39700</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,175 +1748,179 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-139400</v>
+        <v>-145100</v>
       </c>
       <c r="E20" s="3">
-        <v>-178500</v>
+        <v>-135600</v>
       </c>
       <c r="F20" s="3">
-        <v>-178900</v>
+        <v>-173600</v>
       </c>
       <c r="G20" s="3">
-        <v>-182700</v>
+        <v>-174000</v>
       </c>
       <c r="H20" s="3">
-        <v>-144800</v>
+        <v>-177700</v>
       </c>
       <c r="I20" s="3">
-        <v>-224500</v>
+        <v>-140900</v>
       </c>
       <c r="J20" s="3">
+        <v>-218400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-124900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-259800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-173000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-522600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-308900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>146700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-29500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-18200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
         <v>14400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>155800</v>
+        <v>165400</v>
       </c>
       <c r="E21" s="3">
-        <v>196800</v>
+        <v>151600</v>
       </c>
       <c r="F21" s="3">
-        <v>151100</v>
+        <v>191500</v>
       </c>
       <c r="G21" s="3">
-        <v>134800</v>
+        <v>147000</v>
       </c>
       <c r="H21" s="3">
-        <v>116300</v>
+        <v>131100</v>
       </c>
       <c r="I21" s="3">
-        <v>90900</v>
+        <v>113100</v>
       </c>
       <c r="J21" s="3">
+        <v>88400</v>
+      </c>
+      <c r="K21" s="3">
         <v>111700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-19900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-106600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-216100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>146500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>66400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>82300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>84700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>43600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>56800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>77600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>59000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>45800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>51400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>37000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28700</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1893,59 +1930,62 @@
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26200</v>
+        <v>7900</v>
       </c>
       <c r="E22" s="3">
-        <v>19600</v>
+        <v>25500</v>
       </c>
       <c r="F22" s="3">
-        <v>16900</v>
+        <v>19100</v>
       </c>
       <c r="G22" s="3">
-        <v>15800</v>
+        <v>16400</v>
       </c>
       <c r="H22" s="3">
-        <v>20400</v>
+        <v>15400</v>
       </c>
       <c r="I22" s="3">
-        <v>25400</v>
+        <v>19800</v>
       </c>
       <c r="J22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="K22" s="3">
         <v>28500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>37500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9400</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1955,18 +1995,18 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>89400</v>
+        <v>117100</v>
       </c>
       <c r="E23" s="3">
-        <v>136400</v>
+        <v>87000</v>
       </c>
       <c r="F23" s="3">
-        <v>93000</v>
+        <v>132700</v>
       </c>
       <c r="G23" s="3">
-        <v>78000</v>
+        <v>90500</v>
       </c>
       <c r="H23" s="3">
-        <v>56700</v>
+        <v>75900</v>
       </c>
       <c r="I23" s="3">
-        <v>25800</v>
+        <v>55100</v>
       </c>
       <c r="J23" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K23" s="3">
         <v>45500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-96900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-58100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-163600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-287600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>112800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>68900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>72700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>31300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>67000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>50600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>39200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>45800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>20400</v>
+        <v>27600</v>
       </c>
       <c r="E24" s="3">
-        <v>15200</v>
+        <v>19800</v>
       </c>
       <c r="F24" s="3">
-        <v>17000</v>
+        <v>14700</v>
       </c>
       <c r="G24" s="3">
-        <v>21300</v>
+        <v>16600</v>
       </c>
       <c r="H24" s="3">
-        <v>15000</v>
+        <v>20700</v>
       </c>
       <c r="I24" s="3">
-        <v>11200</v>
+        <v>14600</v>
       </c>
       <c r="J24" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K24" s="3">
         <v>9100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-33700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>5200</v>
       </c>
       <c r="AB24" s="3">
         <v>5200</v>
       </c>
       <c r="AC24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>69000</v>
+        <v>89600</v>
       </c>
       <c r="E26" s="3">
-        <v>121200</v>
+        <v>67100</v>
       </c>
       <c r="F26" s="3">
-        <v>76000</v>
+        <v>117900</v>
       </c>
       <c r="G26" s="3">
-        <v>56800</v>
+        <v>73900</v>
       </c>
       <c r="H26" s="3">
-        <v>41700</v>
+        <v>55200</v>
       </c>
       <c r="I26" s="3">
-        <v>14600</v>
+        <v>40600</v>
       </c>
       <c r="J26" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K26" s="3">
         <v>36400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-62700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-161800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-253800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>101900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>57300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>48800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>48800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>35300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>32200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>22700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>16700</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>68900</v>
+        <v>89200</v>
       </c>
       <c r="E27" s="3">
-        <v>120300</v>
+        <v>67000</v>
       </c>
       <c r="F27" s="3">
-        <v>75500</v>
+        <v>117100</v>
       </c>
       <c r="G27" s="3">
-        <v>56400</v>
+        <v>73500</v>
       </c>
       <c r="H27" s="3">
-        <v>41900</v>
+        <v>54900</v>
       </c>
       <c r="I27" s="3">
-        <v>14600</v>
+        <v>40700</v>
       </c>
       <c r="J27" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K27" s="3">
         <v>37400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-97700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-62800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-160400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-252100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>102500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>58700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>49900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>48600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>33100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>22700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>139400</v>
+        <v>145100</v>
       </c>
       <c r="E32" s="3">
-        <v>178500</v>
+        <v>135600</v>
       </c>
       <c r="F32" s="3">
-        <v>178900</v>
+        <v>173600</v>
       </c>
       <c r="G32" s="3">
-        <v>182700</v>
+        <v>174000</v>
       </c>
       <c r="H32" s="3">
-        <v>144800</v>
+        <v>177700</v>
       </c>
       <c r="I32" s="3">
-        <v>224500</v>
+        <v>140900</v>
       </c>
       <c r="J32" s="3">
+        <v>218400</v>
+      </c>
+      <c r="K32" s="3">
         <v>124900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>259800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>173000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>522600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>308900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-146700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>29500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>18200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>12500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>13400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15400</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>68900</v>
+        <v>89200</v>
       </c>
       <c r="E33" s="3">
-        <v>120300</v>
+        <v>67000</v>
       </c>
       <c r="F33" s="3">
-        <v>75500</v>
+        <v>117100</v>
       </c>
       <c r="G33" s="3">
-        <v>56400</v>
+        <v>73500</v>
       </c>
       <c r="H33" s="3">
-        <v>41900</v>
+        <v>54900</v>
       </c>
       <c r="I33" s="3">
-        <v>14600</v>
+        <v>40700</v>
       </c>
       <c r="J33" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K33" s="3">
         <v>37400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-97700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-62800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-160400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-252100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>102500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>58700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>49900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>48600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>68900</v>
+        <v>89200</v>
       </c>
       <c r="E35" s="3">
-        <v>120300</v>
+        <v>67000</v>
       </c>
       <c r="F35" s="3">
-        <v>75500</v>
+        <v>117100</v>
       </c>
       <c r="G35" s="3">
-        <v>56400</v>
+        <v>73500</v>
       </c>
       <c r="H35" s="3">
-        <v>41900</v>
+        <v>54900</v>
       </c>
       <c r="I35" s="3">
-        <v>14600</v>
+        <v>40700</v>
       </c>
       <c r="J35" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K35" s="3">
         <v>37400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-97700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-62800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-160400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-252100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>102500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>58700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>49900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>48600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,86 +3438,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>921600</v>
+        <v>852500</v>
       </c>
       <c r="E41" s="3">
-        <v>402100</v>
+        <v>896600</v>
       </c>
       <c r="F41" s="3">
-        <v>682300</v>
+        <v>391200</v>
       </c>
       <c r="G41" s="3">
-        <v>407000</v>
+        <v>663800</v>
       </c>
       <c r="H41" s="3">
-        <v>342800</v>
+        <v>395900</v>
       </c>
       <c r="I41" s="3">
-        <v>279500</v>
+        <v>333500</v>
       </c>
       <c r="J41" s="3">
+        <v>271900</v>
+      </c>
+      <c r="K41" s="3">
         <v>432900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>759000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>835700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>907400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>612600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1137100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>360800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>457800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>429000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>543400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>299300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>178900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>45300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>53200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>33400</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3444,86 +3531,89 @@
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1308800</v>
+        <v>1271500</v>
       </c>
       <c r="E42" s="3">
-        <v>1825300</v>
+        <v>1273200</v>
       </c>
       <c r="F42" s="3">
-        <v>1223000</v>
+        <v>1775600</v>
       </c>
       <c r="G42" s="3">
-        <v>1402800</v>
+        <v>1189700</v>
       </c>
       <c r="H42" s="3">
-        <v>1345800</v>
+        <v>1364600</v>
       </c>
       <c r="I42" s="3">
-        <v>1369900</v>
+        <v>1309100</v>
       </c>
       <c r="J42" s="3">
+        <v>1332600</v>
+      </c>
+      <c r="K42" s="3">
         <v>1069800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>498700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>505900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>402300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>452300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>968100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1679500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1520700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1601800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>154300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>474300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>542500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>522600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>507400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>497800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>494300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>26300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>48800</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3536,86 +3626,89 @@
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5076800</v>
+        <v>5134400</v>
       </c>
       <c r="E43" s="3">
-        <v>4565700</v>
+        <v>4938600</v>
       </c>
       <c r="F43" s="3">
-        <v>4010600</v>
+        <v>4441400</v>
       </c>
       <c r="G43" s="3">
-        <v>3540800</v>
+        <v>3901400</v>
       </c>
       <c r="H43" s="3">
-        <v>3610600</v>
+        <v>3444400</v>
       </c>
       <c r="I43" s="3">
-        <v>3941000</v>
+        <v>3512300</v>
       </c>
       <c r="J43" s="3">
+        <v>3833700</v>
+      </c>
+      <c r="K43" s="3">
         <v>3594600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3681400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3862800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4115000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4000100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3562700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3331500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3326300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3393000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2683200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2593100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2653500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2338800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2375200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1971100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1667400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,86 +3816,89 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>71600</v>
+        <v>83000</v>
       </c>
       <c r="E45" s="3">
-        <v>71100</v>
+        <v>69600</v>
       </c>
       <c r="F45" s="3">
-        <v>74600</v>
+        <v>69200</v>
       </c>
       <c r="G45" s="3">
-        <v>79500</v>
+        <v>72600</v>
       </c>
       <c r="H45" s="3">
-        <v>71300</v>
+        <v>77400</v>
       </c>
       <c r="I45" s="3">
-        <v>74200</v>
+        <v>69300</v>
       </c>
       <c r="J45" s="3">
+        <v>72200</v>
+      </c>
+      <c r="K45" s="3">
         <v>75900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>659900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>591100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>619300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>443700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>248600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>206600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>172200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>123600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>82800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>28000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3812,86 +3911,89 @@
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7378900</v>
+        <v>7341400</v>
       </c>
       <c r="E46" s="3">
-        <v>6864300</v>
+        <v>7178000</v>
       </c>
       <c r="F46" s="3">
-        <v>5990500</v>
+        <v>6677400</v>
       </c>
       <c r="G46" s="3">
-        <v>5430100</v>
+        <v>5827400</v>
       </c>
       <c r="H46" s="3">
-        <v>5370500</v>
+        <v>5282300</v>
       </c>
       <c r="I46" s="3">
-        <v>5664600</v>
+        <v>5224300</v>
       </c>
       <c r="J46" s="3">
+        <v>5510400</v>
+      </c>
+      <c r="K46" s="3">
         <v>5173200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5598900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5795500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6044000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5508700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5916500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5578400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5477000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5547500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3463800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3417800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3399400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2934700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2921800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2492300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2218900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3904,86 +4006,89 @@
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>61400</v>
+        <v>59500</v>
       </c>
       <c r="E47" s="3">
-        <v>52100</v>
+        <v>59700</v>
       </c>
       <c r="F47" s="3">
-        <v>51900</v>
+        <v>50700</v>
       </c>
       <c r="G47" s="3">
-        <v>47300</v>
+        <v>50500</v>
       </c>
       <c r="H47" s="3">
-        <v>46600</v>
+        <v>46000</v>
       </c>
       <c r="I47" s="3">
-        <v>78800</v>
+        <v>45300</v>
       </c>
       <c r="J47" s="3">
+        <v>76600</v>
+      </c>
+      <c r="K47" s="3">
         <v>91100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>75400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>209000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>276400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>435900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>694500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>81200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,86 +4101,89 @@
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>313800</v>
+        <v>310600</v>
       </c>
       <c r="E48" s="3">
-        <v>307100</v>
+        <v>305300</v>
       </c>
       <c r="F48" s="3">
-        <v>305900</v>
+        <v>298700</v>
       </c>
       <c r="G48" s="3">
-        <v>314200</v>
+        <v>297600</v>
       </c>
       <c r="H48" s="3">
-        <v>330800</v>
+        <v>305600</v>
       </c>
       <c r="I48" s="3">
-        <v>303200</v>
+        <v>321800</v>
       </c>
       <c r="J48" s="3">
+        <v>295000</v>
+      </c>
+      <c r="K48" s="3">
         <v>303500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>336800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>329100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>316800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>262100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>188200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>172800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>134200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>126500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>117700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>101300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>88500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>70500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>62800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>47500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>46800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>57400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4088,86 +4196,89 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1624300</v>
+        <v>1600500</v>
       </c>
       <c r="E49" s="3">
-        <v>1624900</v>
+        <v>1580000</v>
       </c>
       <c r="F49" s="3">
-        <v>1613500</v>
+        <v>1580700</v>
       </c>
       <c r="G49" s="3">
-        <v>1606900</v>
+        <v>1569500</v>
       </c>
       <c r="H49" s="3">
-        <v>1594000</v>
+        <v>1563200</v>
       </c>
       <c r="I49" s="3">
-        <v>1594900</v>
+        <v>1550600</v>
       </c>
       <c r="J49" s="3">
+        <v>1551500</v>
+      </c>
+      <c r="K49" s="3">
         <v>1588700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1721100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1692800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1673300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1655300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>220700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>205200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>194600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>151500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>135900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>75200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>69000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>67800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>60700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>58500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>54900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>56800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>55900</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,86 +4481,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>157600</v>
+        <v>159800</v>
       </c>
       <c r="E52" s="3">
-        <v>148200</v>
+        <v>153300</v>
       </c>
       <c r="F52" s="3">
-        <v>136800</v>
+        <v>144100</v>
       </c>
       <c r="G52" s="3">
-        <v>130600</v>
+        <v>133100</v>
       </c>
       <c r="H52" s="3">
-        <v>143000</v>
+        <v>127100</v>
       </c>
       <c r="I52" s="3">
-        <v>163800</v>
+        <v>139100</v>
       </c>
       <c r="J52" s="3">
+        <v>159300</v>
+      </c>
+      <c r="K52" s="3">
         <v>183800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>186900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>161700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>189000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>135800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>109100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>51500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>50200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>46400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>49600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>46600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>51200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>51900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>48400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>46800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>54500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,86 +4671,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9535900</v>
+        <v>9471700</v>
       </c>
       <c r="E54" s="3">
-        <v>8996600</v>
+        <v>9276300</v>
       </c>
       <c r="F54" s="3">
-        <v>8098700</v>
+        <v>8751700</v>
       </c>
       <c r="G54" s="3">
-        <v>7529100</v>
+        <v>7878200</v>
       </c>
       <c r="H54" s="3">
-        <v>7484900</v>
+        <v>7324100</v>
       </c>
       <c r="I54" s="3">
-        <v>7805300</v>
+        <v>7281100</v>
       </c>
       <c r="J54" s="3">
+        <v>7592800</v>
+      </c>
+      <c r="K54" s="3">
         <v>7340400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7919100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8188100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8496900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7997900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7129000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6132700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5939900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5888100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3769200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3669500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3621200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3143000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3109300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2667700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2371500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,86 +4838,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3606400</v>
+        <v>3414600</v>
       </c>
       <c r="E57" s="3">
-        <v>3635600</v>
+        <v>3508200</v>
       </c>
       <c r="F57" s="3">
-        <v>3265000</v>
+        <v>3536600</v>
       </c>
       <c r="G57" s="3">
-        <v>2947600</v>
+        <v>3176100</v>
       </c>
       <c r="H57" s="3">
-        <v>2961800</v>
+        <v>2867300</v>
       </c>
       <c r="I57" s="3">
-        <v>3173200</v>
+        <v>2881200</v>
       </c>
       <c r="J57" s="3">
+        <v>3086800</v>
+      </c>
+      <c r="K57" s="3">
         <v>2812000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3075300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3248800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2991400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2156500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1673900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1749800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1691700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1382700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1118700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1218600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1073100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1105200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1088800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>912300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>865300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>940200</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4800,86 +4931,89 @@
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>412200</v>
+        <v>546000</v>
       </c>
       <c r="E58" s="3">
-        <v>347300</v>
+        <v>401000</v>
       </c>
       <c r="F58" s="3">
-        <v>363900</v>
+        <v>337900</v>
       </c>
       <c r="G58" s="3">
-        <v>352800</v>
+        <v>354000</v>
       </c>
       <c r="H58" s="3">
-        <v>356600</v>
+        <v>343200</v>
       </c>
       <c r="I58" s="3">
-        <v>521500</v>
+        <v>346900</v>
       </c>
       <c r="J58" s="3">
+        <v>507300</v>
+      </c>
+      <c r="K58" s="3">
         <v>462000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>681200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>889600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>781800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>572100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>672500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>656700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>588400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>570000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>739900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>839400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>930600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>512800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>398400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>246700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>138700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3900</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4892,86 +5026,89 @@
       <c r="AF58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1391600</v>
+        <v>1439900</v>
       </c>
       <c r="E59" s="3">
-        <v>1401400</v>
+        <v>1353700</v>
       </c>
       <c r="F59" s="3">
-        <v>1087700</v>
+        <v>1363300</v>
       </c>
       <c r="G59" s="3">
-        <v>968900</v>
+        <v>1058100</v>
       </c>
       <c r="H59" s="3">
-        <v>940100</v>
+        <v>942600</v>
       </c>
       <c r="I59" s="3">
-        <v>956400</v>
+        <v>914600</v>
       </c>
       <c r="J59" s="3">
+        <v>930400</v>
+      </c>
+      <c r="K59" s="3">
         <v>803600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>740000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>701100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>569300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>422000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>210700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>171300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>165100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>125200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>86200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>57700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>33500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>35700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>29100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27900</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4984,86 +5121,89 @@
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5410200</v>
+        <v>5400600</v>
       </c>
       <c r="E60" s="3">
-        <v>5384400</v>
+        <v>5262900</v>
       </c>
       <c r="F60" s="3">
-        <v>4716500</v>
+        <v>5237800</v>
       </c>
       <c r="G60" s="3">
-        <v>4269300</v>
+        <v>4588100</v>
       </c>
       <c r="H60" s="3">
-        <v>4258600</v>
+        <v>4153100</v>
       </c>
       <c r="I60" s="3">
-        <v>4651200</v>
+        <v>4142600</v>
       </c>
       <c r="J60" s="3">
+        <v>4524500</v>
+      </c>
+      <c r="K60" s="3">
         <v>4077700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1500500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4666000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4599900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3985500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3039800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2502000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2503300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2386800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2208700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2015800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2192900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1619400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1539300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1370300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1080200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>923000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>972100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5076,86 +5216,89 @@
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1118700</v>
+        <v>1119500</v>
       </c>
       <c r="E61" s="3">
-        <v>672400</v>
+        <v>1088200</v>
       </c>
       <c r="F61" s="3">
-        <v>504200</v>
+        <v>654100</v>
       </c>
       <c r="G61" s="3">
-        <v>467000</v>
+        <v>490500</v>
       </c>
       <c r="H61" s="3">
-        <v>491400</v>
+        <v>454300</v>
       </c>
       <c r="I61" s="3">
-        <v>504100</v>
+        <v>478000</v>
       </c>
       <c r="J61" s="3">
+        <v>490400</v>
+      </c>
+      <c r="K61" s="3">
         <v>638000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>680400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>630100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>906000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>860300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1044200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>560400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>549800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>582500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>241400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>397800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>315400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>462600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>531100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>295800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>367400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>381000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>481100</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5168,86 +5311,89 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>234800</v>
+        <v>216400</v>
       </c>
       <c r="E62" s="3">
-        <v>228300</v>
+        <v>228400</v>
       </c>
       <c r="F62" s="3">
-        <v>260100</v>
+        <v>222100</v>
       </c>
       <c r="G62" s="3">
-        <v>251700</v>
+        <v>253000</v>
       </c>
       <c r="H62" s="3">
-        <v>261000</v>
+        <v>244800</v>
       </c>
       <c r="I62" s="3">
-        <v>257300</v>
+        <v>253900</v>
       </c>
       <c r="J62" s="3">
+        <v>250300</v>
+      </c>
+      <c r="K62" s="3">
         <v>266800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3201800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>209800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>240400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>227700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>111300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>89400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>81800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>61100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>51000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>19700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18800</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,86 +5691,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6773400</v>
+        <v>6746400</v>
       </c>
       <c r="E66" s="3">
-        <v>6295000</v>
+        <v>6589000</v>
       </c>
       <c r="F66" s="3">
-        <v>5491100</v>
+        <v>6123600</v>
       </c>
       <c r="G66" s="3">
-        <v>4998300</v>
+        <v>5341600</v>
       </c>
       <c r="H66" s="3">
-        <v>5021300</v>
+        <v>4862200</v>
       </c>
       <c r="I66" s="3">
-        <v>5423000</v>
+        <v>4884500</v>
       </c>
       <c r="J66" s="3">
+        <v>5275400</v>
+      </c>
+      <c r="K66" s="3">
         <v>4997100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5399800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5528800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5764700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5090800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4210900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3163600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3160900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3048700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2519400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2442000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2518100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2102100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2090000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1681600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1462900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,86 +6201,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2883700</v>
+        <v>2897700</v>
       </c>
       <c r="E72" s="3">
-        <v>2813000</v>
+        <v>2805200</v>
       </c>
       <c r="F72" s="3">
-        <v>2669400</v>
+        <v>2736500</v>
       </c>
       <c r="G72" s="3">
-        <v>2586200</v>
+        <v>2596800</v>
       </c>
       <c r="H72" s="3">
-        <v>2526300</v>
+        <v>2515800</v>
       </c>
       <c r="I72" s="3">
-        <v>2475000</v>
+        <v>2457500</v>
       </c>
       <c r="J72" s="3">
+        <v>2407600</v>
+      </c>
+      <c r="K72" s="3">
         <v>2430900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2614100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2732500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2954400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3096800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3211200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2986400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2794100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2861600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1274000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1250900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1116500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1055200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1034600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>998300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>918700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>132900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>175600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,86 +6581,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2762500</v>
+        <v>2725400</v>
       </c>
       <c r="E76" s="3">
-        <v>2701600</v>
+        <v>2687300</v>
       </c>
       <c r="F76" s="3">
-        <v>2607600</v>
+        <v>2628100</v>
       </c>
       <c r="G76" s="3">
-        <v>2530800</v>
+        <v>2536600</v>
       </c>
       <c r="H76" s="3">
-        <v>2463600</v>
+        <v>2461900</v>
       </c>
       <c r="I76" s="3">
-        <v>2382300</v>
+        <v>2396600</v>
       </c>
       <c r="J76" s="3">
+        <v>2317400</v>
+      </c>
+      <c r="K76" s="3">
         <v>2343300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2519300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2659300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2732200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2907100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2918100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2969000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2778900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2839400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1249900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1227500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1103100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1040900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1019300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>986200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>908600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>126900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>167300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>68900</v>
+        <v>89200</v>
       </c>
       <c r="E81" s="3">
-        <v>120300</v>
+        <v>67000</v>
       </c>
       <c r="F81" s="3">
-        <v>75500</v>
+        <v>117100</v>
       </c>
       <c r="G81" s="3">
-        <v>56400</v>
+        <v>73500</v>
       </c>
       <c r="H81" s="3">
-        <v>41900</v>
+        <v>54900</v>
       </c>
       <c r="I81" s="3">
-        <v>14600</v>
+        <v>40700</v>
       </c>
       <c r="J81" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K81" s="3">
         <v>37400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-97700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-62800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-160400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-252100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>102500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>58700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>49900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>48600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>40200</v>
+        <v>40300</v>
       </c>
       <c r="E83" s="3">
-        <v>40800</v>
+        <v>39100</v>
       </c>
       <c r="F83" s="3">
-        <v>41200</v>
+        <v>39700</v>
       </c>
       <c r="G83" s="3">
-        <v>41000</v>
+        <v>40100</v>
       </c>
       <c r="H83" s="3">
-        <v>39300</v>
+        <v>39800</v>
       </c>
       <c r="I83" s="3">
-        <v>39700</v>
+        <v>38200</v>
       </c>
       <c r="J83" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K83" s="3">
         <v>37700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>22500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4400</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-456900</v>
+        <v>-128700</v>
       </c>
       <c r="E89" s="3">
-        <v>-77000</v>
+        <v>-444500</v>
       </c>
       <c r="F89" s="3">
-        <v>11700</v>
+        <v>-74900</v>
       </c>
       <c r="G89" s="3">
-        <v>153800</v>
+        <v>11400</v>
       </c>
       <c r="H89" s="3">
-        <v>215900</v>
+        <v>149600</v>
       </c>
       <c r="I89" s="3">
-        <v>63400</v>
+        <v>210000</v>
       </c>
       <c r="J89" s="3">
+        <v>61700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-31200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>143200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>159400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>120100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>358300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>256000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>45400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-326800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>219400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>71400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-122500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>35100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-353300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-55200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-379200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-344600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-306600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-285300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-176400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-332200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-416400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-155300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-109300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-216800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-241800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-546400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-151300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-64800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-17800</v>
       </c>
       <c r="T91" s="3">
         <v>-17800</v>
       </c>
       <c r="U91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="V91" s="3">
         <v>-3600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>498900</v>
+        <v>-12000</v>
       </c>
       <c r="E94" s="3">
-        <v>-315100</v>
+        <v>485300</v>
       </c>
       <c r="F94" s="3">
-        <v>243200</v>
+        <v>-306500</v>
       </c>
       <c r="G94" s="3">
-        <v>-93900</v>
+        <v>236600</v>
       </c>
       <c r="H94" s="3">
-        <v>9500</v>
+        <v>-91300</v>
       </c>
       <c r="I94" s="3">
-        <v>-153900</v>
+        <v>9300</v>
       </c>
       <c r="J94" s="3">
+        <v>-149700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-51100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-150500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-51200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-596400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>167200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>282300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>97400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-55100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>16900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-470400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>4300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>26700</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>477500</v>
+        <v>93000</v>
       </c>
       <c r="E100" s="3">
-        <v>113100</v>
+        <v>464500</v>
       </c>
       <c r="F100" s="3">
-        <v>20500</v>
+        <v>110000</v>
       </c>
       <c r="G100" s="3">
-        <v>2900</v>
+        <v>19900</v>
       </c>
       <c r="H100" s="3">
-        <v>-163900</v>
+        <v>2800</v>
       </c>
       <c r="I100" s="3">
-        <v>-64900</v>
+        <v>-159500</v>
       </c>
       <c r="J100" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-183300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-222700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-71400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>225100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-328900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>345300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>29800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1704200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-255100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-60000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>279100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>35200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>387000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>870200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>229100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J101" s="3">
         <v>1900</v>
       </c>
-      <c r="I101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-500</v>
       </c>
       <c r="T101" s="3">
         <v>-500</v>
       </c>
       <c r="U101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>519500</v>
+        <v>-44100</v>
       </c>
       <c r="E102" s="3">
-        <v>-280200</v>
+        <v>505400</v>
       </c>
       <c r="F102" s="3">
-        <v>275400</v>
+        <v>-272600</v>
       </c>
       <c r="G102" s="3">
-        <v>64100</v>
+        <v>267900</v>
       </c>
       <c r="H102" s="3">
-        <v>63400</v>
+        <v>62400</v>
       </c>
       <c r="I102" s="3">
-        <v>-153500</v>
+        <v>61600</v>
       </c>
       <c r="J102" s="3">
+        <v>-149300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-266700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-76700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>293400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-570100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>776300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-113000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>47600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>246200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>108400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>133600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>125900</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>576200</v>
+        <v>590100</v>
       </c>
       <c r="E8" s="3">
-        <v>554400</v>
+        <v>556100</v>
       </c>
       <c r="F8" s="3">
-        <v>606700</v>
+        <v>587700</v>
       </c>
       <c r="G8" s="3">
-        <v>564300</v>
+        <v>638400</v>
       </c>
       <c r="H8" s="3">
-        <v>531100</v>
+        <v>591300</v>
       </c>
       <c r="I8" s="3">
-        <v>487400</v>
+        <v>572400</v>
       </c>
       <c r="J8" s="3">
+        <v>504200</v>
+      </c>
+      <c r="K8" s="3">
         <v>545000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>463500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>461800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>414900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>641700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>296000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>118800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>168000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>185000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>182800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>130600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>141300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>144600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>124000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>110000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>100300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>94400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>76600</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>18900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>18400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>151200</v>
+        <v>157800</v>
       </c>
       <c r="E9" s="3">
-        <v>145600</v>
+        <v>151600</v>
       </c>
       <c r="F9" s="3">
-        <v>144300</v>
+        <v>161500</v>
       </c>
       <c r="G9" s="3">
-        <v>139000</v>
+        <v>165400</v>
       </c>
       <c r="H9" s="3">
-        <v>123200</v>
+        <v>154900</v>
       </c>
       <c r="I9" s="3">
-        <v>129600</v>
+        <v>142100</v>
       </c>
       <c r="J9" s="3">
+        <v>142400</v>
+      </c>
+      <c r="K9" s="3">
         <v>125400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>124000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>125500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>135200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>130400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>105900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>58600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>46400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>38900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>23700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>425000</v>
+        <v>432400</v>
       </c>
       <c r="E10" s="3">
-        <v>408900</v>
+        <v>404600</v>
       </c>
       <c r="F10" s="3">
-        <v>462500</v>
+        <v>426200</v>
       </c>
       <c r="G10" s="3">
-        <v>425300</v>
+        <v>473000</v>
       </c>
       <c r="H10" s="3">
-        <v>407900</v>
+        <v>436400</v>
       </c>
       <c r="I10" s="3">
-        <v>357700</v>
+        <v>430300</v>
       </c>
       <c r="J10" s="3">
+        <v>361800</v>
+      </c>
+      <c r="K10" s="3">
         <v>419600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>339400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>336300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>279800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>511300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>190100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>121600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>145100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>142100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>91700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>111700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>120900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>103200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>91100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>84300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>76400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>61700</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="3">
         <v>5200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1316,8 +1336,8 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -1325,8 +1345,8 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>-6000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1337,21 +1357,21 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1361,8 +1381,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1397,80 +1417,83 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9300</v>
+        <v>33500</v>
       </c>
       <c r="E15" s="3">
-        <v>10000</v>
+        <v>30500</v>
       </c>
       <c r="F15" s="3">
-        <v>10500</v>
+        <v>32000</v>
       </c>
       <c r="G15" s="3">
-        <v>12500</v>
+        <v>32900</v>
       </c>
       <c r="H15" s="3">
-        <v>12700</v>
+        <v>44600</v>
       </c>
       <c r="I15" s="3">
-        <v>13100</v>
+        <v>46000</v>
       </c>
       <c r="J15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>3700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2500</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1480,8 +1503,8 @@
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>306000</v>
+        <v>326400</v>
       </c>
       <c r="E17" s="3">
-        <v>306400</v>
+        <v>306700</v>
       </c>
       <c r="F17" s="3">
-        <v>281400</v>
+        <v>339900</v>
       </c>
       <c r="G17" s="3">
-        <v>283400</v>
+        <v>322700</v>
       </c>
       <c r="H17" s="3">
-        <v>262000</v>
+        <v>315700</v>
       </c>
       <c r="I17" s="3">
-        <v>271500</v>
+        <v>302300</v>
       </c>
       <c r="J17" s="3">
+        <v>298400</v>
+      </c>
+      <c r="K17" s="3">
         <v>276800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>264600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>261400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>266200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>248200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>246300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>137800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>108700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>105800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>97300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>86800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>66800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>54800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>55900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>42000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>49000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="3">
         <v>36000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>28600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>270200</v>
+        <v>263700</v>
       </c>
       <c r="E18" s="3">
-        <v>248100</v>
+        <v>249400</v>
       </c>
       <c r="F18" s="3">
-        <v>325300</v>
+        <v>247800</v>
       </c>
       <c r="G18" s="3">
-        <v>280900</v>
+        <v>315800</v>
       </c>
       <c r="H18" s="3">
-        <v>269000</v>
+        <v>275500</v>
       </c>
       <c r="I18" s="3">
-        <v>215800</v>
+        <v>270100</v>
       </c>
       <c r="J18" s="3">
+        <v>205900</v>
+      </c>
+      <c r="K18" s="3">
         <v>268200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>198900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>148700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>393500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>59300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>79200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>85600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>74400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>86900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>69100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>54100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>58300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>45400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>39700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,181 +1782,185 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-145100</v>
+        <v>89100</v>
       </c>
       <c r="E20" s="3">
-        <v>-135600</v>
+        <v>86000</v>
       </c>
       <c r="F20" s="3">
-        <v>-173600</v>
+        <v>111100</v>
       </c>
       <c r="G20" s="3">
-        <v>-174000</v>
+        <v>127500</v>
       </c>
       <c r="H20" s="3">
-        <v>-177700</v>
+        <v>140900</v>
       </c>
       <c r="I20" s="3">
-        <v>-140900</v>
+        <v>148300</v>
       </c>
       <c r="J20" s="3">
+        <v>114500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-218400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-124900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-259800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-173000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-522600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-308900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>146700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-29500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>14400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>165400</v>
+        <v>208100</v>
       </c>
       <c r="E21" s="3">
-        <v>151600</v>
+        <v>193900</v>
       </c>
       <c r="F21" s="3">
-        <v>191500</v>
+        <v>168700</v>
       </c>
       <c r="G21" s="3">
-        <v>147000</v>
+        <v>221200</v>
       </c>
       <c r="H21" s="3">
-        <v>131100</v>
+        <v>179300</v>
       </c>
       <c r="I21" s="3">
-        <v>113100</v>
+        <v>167700</v>
       </c>
       <c r="J21" s="3">
+        <v>133300</v>
+      </c>
+      <c r="K21" s="3">
         <v>88400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>111700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-19900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-106600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-216100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>146500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>66400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>82300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>84700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>43600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>56800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>59000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>51400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>37000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28700</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1933,62 +1970,65 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>6900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7900</v>
+        <v>51600</v>
       </c>
       <c r="E22" s="3">
-        <v>25500</v>
+        <v>46000</v>
       </c>
       <c r="F22" s="3">
-        <v>19100</v>
+        <v>40200</v>
       </c>
       <c r="G22" s="3">
-        <v>16400</v>
+        <v>36200</v>
       </c>
       <c r="H22" s="3">
-        <v>15400</v>
+        <v>33800</v>
       </c>
       <c r="I22" s="3">
-        <v>19800</v>
+        <v>34200</v>
       </c>
       <c r="J22" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K22" s="3">
         <v>24800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1998,18 +2038,18 @@
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>117100</v>
+        <v>123000</v>
       </c>
       <c r="E23" s="3">
-        <v>87000</v>
+        <v>117400</v>
       </c>
       <c r="F23" s="3">
-        <v>132700</v>
+        <v>96500</v>
       </c>
       <c r="G23" s="3">
-        <v>90500</v>
+        <v>152100</v>
       </c>
       <c r="H23" s="3">
-        <v>75900</v>
+        <v>100800</v>
       </c>
       <c r="I23" s="3">
-        <v>55100</v>
+        <v>87600</v>
       </c>
       <c r="J23" s="3">
+        <v>60600</v>
+      </c>
+      <c r="K23" s="3">
         <v>25100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-96900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-58100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-163600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-287600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>112800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>40700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>68900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>72700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>31300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>67000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>50600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>45800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>32000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>24200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E24" s="3">
         <v>27600</v>
       </c>
-      <c r="E24" s="3">
-        <v>19800</v>
-      </c>
       <c r="F24" s="3">
-        <v>14700</v>
+        <v>22000</v>
       </c>
       <c r="G24" s="3">
-        <v>16600</v>
+        <v>16900</v>
       </c>
       <c r="H24" s="3">
-        <v>20700</v>
+        <v>18500</v>
       </c>
       <c r="I24" s="3">
-        <v>14600</v>
+        <v>23900</v>
       </c>
       <c r="J24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K24" s="3">
         <v>10900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-33700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>5200</v>
       </c>
       <c r="AC24" s="3">
         <v>5200</v>
       </c>
       <c r="AD24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>89600</v>
+        <v>99700</v>
       </c>
       <c r="E26" s="3">
-        <v>67100</v>
+        <v>89800</v>
       </c>
       <c r="F26" s="3">
-        <v>117900</v>
+        <v>74500</v>
       </c>
       <c r="G26" s="3">
-        <v>73900</v>
+        <v>135200</v>
       </c>
       <c r="H26" s="3">
-        <v>55200</v>
+        <v>82400</v>
       </c>
       <c r="I26" s="3">
-        <v>40600</v>
+        <v>63700</v>
       </c>
       <c r="J26" s="3">
+        <v>44600</v>
+      </c>
+      <c r="K26" s="3">
         <v>14200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-98100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-62700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-161800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-253800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>101900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>57300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>48800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>48800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>35300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>32200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>16700</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>89200</v>
+        <v>99100</v>
       </c>
       <c r="E27" s="3">
-        <v>67000</v>
+        <v>89400</v>
       </c>
       <c r="F27" s="3">
-        <v>117100</v>
+        <v>74400</v>
       </c>
       <c r="G27" s="3">
-        <v>73500</v>
+        <v>134200</v>
       </c>
       <c r="H27" s="3">
-        <v>54900</v>
+        <v>81800</v>
       </c>
       <c r="I27" s="3">
-        <v>40700</v>
+        <v>63300</v>
       </c>
       <c r="J27" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K27" s="3">
         <v>14200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-97700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-62800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-160400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-252100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>102500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>58700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>48600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>32300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>33100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>16400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>145100</v>
+        <v>-89100</v>
       </c>
       <c r="E32" s="3">
-        <v>135600</v>
+        <v>-86000</v>
       </c>
       <c r="F32" s="3">
-        <v>173600</v>
+        <v>-111100</v>
       </c>
       <c r="G32" s="3">
-        <v>174000</v>
+        <v>-127500</v>
       </c>
       <c r="H32" s="3">
-        <v>177700</v>
+        <v>-140900</v>
       </c>
       <c r="I32" s="3">
-        <v>140900</v>
+        <v>-148300</v>
       </c>
       <c r="J32" s="3">
+        <v>-114500</v>
+      </c>
+      <c r="K32" s="3">
         <v>218400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>124900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>259800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>173000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>522600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>308900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-146700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>29500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>15400</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>89200</v>
+        <v>99100</v>
       </c>
       <c r="E33" s="3">
-        <v>67000</v>
+        <v>89400</v>
       </c>
       <c r="F33" s="3">
-        <v>117100</v>
+        <v>74400</v>
       </c>
       <c r="G33" s="3">
-        <v>73500</v>
+        <v>134200</v>
       </c>
       <c r="H33" s="3">
-        <v>54900</v>
+        <v>81800</v>
       </c>
       <c r="I33" s="3">
-        <v>40700</v>
+        <v>63300</v>
       </c>
       <c r="J33" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K33" s="3">
         <v>14200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-97700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-62800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-160400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-252100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>102500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>58700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>48600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>89200</v>
+        <v>99100</v>
       </c>
       <c r="E35" s="3">
-        <v>67000</v>
+        <v>89400</v>
       </c>
       <c r="F35" s="3">
-        <v>117100</v>
+        <v>74400</v>
       </c>
       <c r="G35" s="3">
-        <v>73500</v>
+        <v>134200</v>
       </c>
       <c r="H35" s="3">
-        <v>54900</v>
+        <v>81800</v>
       </c>
       <c r="I35" s="3">
-        <v>40700</v>
+        <v>63300</v>
       </c>
       <c r="J35" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K35" s="3">
         <v>14200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-97700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-62800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-160400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-252100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>102500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>58700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>48600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,89 +3525,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>852500</v>
+        <v>737000</v>
       </c>
       <c r="E41" s="3">
-        <v>896600</v>
+        <v>854400</v>
       </c>
       <c r="F41" s="3">
-        <v>391200</v>
+        <v>994600</v>
       </c>
       <c r="G41" s="3">
-        <v>663800</v>
+        <v>448500</v>
       </c>
       <c r="H41" s="3">
-        <v>395900</v>
+        <v>739500</v>
       </c>
       <c r="I41" s="3">
-        <v>333500</v>
+        <v>456800</v>
       </c>
       <c r="J41" s="3">
+        <v>366500</v>
+      </c>
+      <c r="K41" s="3">
         <v>271900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>432900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>759000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>835700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>907400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>612600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1137100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>360800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>457800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>429000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>543400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>299300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>178900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>45300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>53200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>33400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3534,89 +3621,92 @@
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1271500</v>
+        <v>68600</v>
       </c>
       <c r="E42" s="3">
-        <v>1273200</v>
+        <v>19200</v>
       </c>
       <c r="F42" s="3">
-        <v>1775600</v>
+        <v>92500</v>
       </c>
       <c r="G42" s="3">
-        <v>1189700</v>
+        <v>717500</v>
       </c>
       <c r="H42" s="3">
-        <v>1364600</v>
+        <v>409000</v>
       </c>
       <c r="I42" s="3">
-        <v>1309100</v>
+        <v>724500</v>
       </c>
       <c r="J42" s="3">
+        <v>643300</v>
+      </c>
+      <c r="K42" s="3">
         <v>1332600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1069800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>498700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>505900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>402300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>452300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>968100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1679500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1520700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1601800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>154300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>474300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>542500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>522600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>507400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>497800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>494300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>26300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>48800</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3629,89 +3719,92 @@
       <c r="AG42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5134400</v>
+        <v>5008400</v>
       </c>
       <c r="E43" s="3">
-        <v>4938600</v>
+        <v>5117400</v>
       </c>
       <c r="F43" s="3">
-        <v>4441400</v>
+        <v>5449000</v>
       </c>
       <c r="G43" s="3">
-        <v>3901400</v>
+        <v>5067800</v>
       </c>
       <c r="H43" s="3">
-        <v>3444400</v>
+        <v>4326600</v>
       </c>
       <c r="I43" s="3">
-        <v>3512300</v>
+        <v>3935400</v>
       </c>
       <c r="J43" s="3">
+        <v>3823300</v>
+      </c>
+      <c r="K43" s="3">
         <v>3833700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3594600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3681400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3862800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4115000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4000100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3562700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3331500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3326300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3393000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2683200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2593100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2653500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2338800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2375200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1971100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3724,31 +3817,34 @@
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3819,89 +3915,92 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>83000</v>
+        <v>1530100</v>
       </c>
       <c r="E45" s="3">
-        <v>69600</v>
+        <v>1366600</v>
       </c>
       <c r="F45" s="3">
-        <v>69200</v>
+        <v>1426800</v>
       </c>
       <c r="G45" s="3">
-        <v>72600</v>
+        <v>1422900</v>
       </c>
       <c r="H45" s="3">
-        <v>77400</v>
+        <v>993200</v>
       </c>
       <c r="I45" s="3">
-        <v>69300</v>
+        <v>952300</v>
       </c>
       <c r="J45" s="3">
+        <v>881200</v>
+      </c>
+      <c r="K45" s="3">
         <v>72200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>75900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>659900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>591100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>619300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>443700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>248600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>206600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>172200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>123600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>82800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>28000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3914,89 +4013,92 @@
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7341400</v>
+        <v>7344100</v>
       </c>
       <c r="E46" s="3">
-        <v>7178000</v>
+        <v>7357600</v>
       </c>
       <c r="F46" s="3">
-        <v>6677400</v>
+        <v>7962900</v>
       </c>
       <c r="G46" s="3">
-        <v>5827400</v>
+        <v>7656700</v>
       </c>
       <c r="H46" s="3">
-        <v>5282300</v>
+        <v>6492300</v>
       </c>
       <c r="I46" s="3">
-        <v>5224300</v>
+        <v>6095400</v>
       </c>
       <c r="J46" s="3">
+        <v>5740600</v>
+      </c>
+      <c r="K46" s="3">
         <v>5510400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5173200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5598900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5795500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6044000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5508700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5916500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5578400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5477000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5547500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3463800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3417800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3399400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2934700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2921800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2492300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4009,89 +4111,92 @@
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>59500</v>
+        <v>20500</v>
       </c>
       <c r="E47" s="3">
-        <v>59700</v>
+        <v>20100</v>
       </c>
       <c r="F47" s="3">
-        <v>50700</v>
+        <v>26400</v>
       </c>
       <c r="G47" s="3">
-        <v>50500</v>
+        <v>26500</v>
       </c>
       <c r="H47" s="3">
-        <v>46000</v>
+        <v>32300</v>
       </c>
       <c r="I47" s="3">
-        <v>45300</v>
+        <v>29100</v>
       </c>
       <c r="J47" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K47" s="3">
         <v>76600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>91100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>75400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>209000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>276400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>435900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>694500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>81200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>82600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4104,89 +4209,92 @@
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>310600</v>
+        <v>327200</v>
       </c>
       <c r="E48" s="3">
-        <v>305300</v>
+        <v>315700</v>
       </c>
       <c r="F48" s="3">
-        <v>298700</v>
+        <v>344300</v>
       </c>
       <c r="G48" s="3">
-        <v>297600</v>
+        <v>348900</v>
       </c>
       <c r="H48" s="3">
-        <v>305600</v>
+        <v>338200</v>
       </c>
       <c r="I48" s="3">
-        <v>321800</v>
+        <v>360400</v>
       </c>
       <c r="J48" s="3">
+        <v>356600</v>
+      </c>
+      <c r="K48" s="3">
         <v>295000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>303500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>336800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>329100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>316800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>262100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>188200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>172800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>134200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>126500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>117200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>101300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>88500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>70500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>62800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>47500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>46800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>57400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4199,89 +4307,92 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1600500</v>
+        <v>1640200</v>
       </c>
       <c r="E49" s="3">
-        <v>1580000</v>
+        <v>1599600</v>
       </c>
       <c r="F49" s="3">
-        <v>1580700</v>
+        <v>1747200</v>
       </c>
       <c r="G49" s="3">
-        <v>1569500</v>
+        <v>1806100</v>
       </c>
       <c r="H49" s="3">
-        <v>1563200</v>
+        <v>1742000</v>
       </c>
       <c r="I49" s="3">
-        <v>1550600</v>
+        <v>1796000</v>
       </c>
       <c r="J49" s="3">
+        <v>1700900</v>
+      </c>
+      <c r="K49" s="3">
         <v>1551500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1588700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1721100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1692800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1673300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1655300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>220700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>205200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>194600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>151500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>135900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>75200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>69000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>67800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>60700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>58500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>54900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>56800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>55900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,89 +4601,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>159800</v>
+        <v>26700</v>
       </c>
       <c r="E52" s="3">
-        <v>153300</v>
+        <v>24000</v>
       </c>
       <c r="F52" s="3">
-        <v>144100</v>
+        <v>34200</v>
       </c>
       <c r="G52" s="3">
-        <v>133100</v>
+        <v>28300</v>
       </c>
       <c r="H52" s="3">
-        <v>127100</v>
+        <v>26400</v>
       </c>
       <c r="I52" s="3">
-        <v>139100</v>
+        <v>30900</v>
       </c>
       <c r="J52" s="3">
+        <v>31100</v>
+      </c>
+      <c r="K52" s="3">
         <v>159300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>183800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>186900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>161700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>189000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>135800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>95100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>50200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>46400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>49600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>51200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>51900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>48400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>46800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>54500</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,89 +4797,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9471700</v>
+        <v>9536000</v>
       </c>
       <c r="E54" s="3">
-        <v>9276300</v>
+        <v>9492700</v>
       </c>
       <c r="F54" s="3">
-        <v>8751700</v>
+        <v>10290600</v>
       </c>
       <c r="G54" s="3">
-        <v>7878200</v>
+        <v>10035200</v>
       </c>
       <c r="H54" s="3">
-        <v>7324100</v>
+        <v>8777000</v>
       </c>
       <c r="I54" s="3">
-        <v>7281100</v>
+        <v>8451500</v>
       </c>
       <c r="J54" s="3">
+        <v>8000700</v>
+      </c>
+      <c r="K54" s="3">
         <v>7592800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7340400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7919100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8188100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8496900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7997900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7129000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6132700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5939900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5888100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3769200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3669500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3621200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3143000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3109300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2667700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,89 +4969,90 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3414600</v>
+        <v>103600</v>
       </c>
       <c r="E57" s="3">
-        <v>3508200</v>
+        <v>94700</v>
       </c>
       <c r="F57" s="3">
-        <v>3536600</v>
+        <v>101800</v>
       </c>
       <c r="G57" s="3">
-        <v>3176100</v>
+        <v>105900</v>
       </c>
       <c r="H57" s="3">
-        <v>2867300</v>
+        <v>90100</v>
       </c>
       <c r="I57" s="3">
-        <v>2881200</v>
+        <v>87800</v>
       </c>
       <c r="J57" s="3">
+        <v>98100</v>
+      </c>
+      <c r="K57" s="3">
         <v>3086800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2812000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>79300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3075300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3248800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2991400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2156500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1673900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1749800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1691700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1382700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1118700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1218600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1073100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1105200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1088800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>912300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>865300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>940200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4934,89 +5065,92 @@
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>546000</v>
+        <v>517300</v>
       </c>
       <c r="E58" s="3">
-        <v>401000</v>
+        <v>547200</v>
       </c>
       <c r="F58" s="3">
-        <v>337900</v>
+        <v>444900</v>
       </c>
       <c r="G58" s="3">
-        <v>354000</v>
+        <v>387400</v>
       </c>
       <c r="H58" s="3">
-        <v>343200</v>
+        <v>394300</v>
       </c>
       <c r="I58" s="3">
-        <v>346900</v>
+        <v>396000</v>
       </c>
       <c r="J58" s="3">
+        <v>381200</v>
+      </c>
+      <c r="K58" s="3">
         <v>507300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>462000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>681200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>889600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>781800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>572100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>672500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>656700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>588400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>570000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>739900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>839400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>930600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>512800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>398400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>246700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>138700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5029,89 +5163,92 @@
       <c r="AG58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1439900</v>
+        <v>4423800</v>
       </c>
       <c r="E59" s="3">
-        <v>1353700</v>
+        <v>4679800</v>
       </c>
       <c r="F59" s="3">
-        <v>1363300</v>
+        <v>5212600</v>
       </c>
       <c r="G59" s="3">
-        <v>1058100</v>
+        <v>5388600</v>
       </c>
       <c r="H59" s="3">
-        <v>942600</v>
+        <v>4516500</v>
       </c>
       <c r="I59" s="3">
-        <v>914600</v>
+        <v>4211500</v>
       </c>
       <c r="J59" s="3">
+        <v>3994000</v>
+      </c>
+      <c r="K59" s="3">
         <v>930400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>803600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>740000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>701100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>569300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>422000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>210700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>171300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>165100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>125200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>86200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>57700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>43600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>33500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>34700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>29100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>46900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5124,89 +5261,92 @@
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5400600</v>
+        <v>5155500</v>
       </c>
       <c r="E60" s="3">
-        <v>5262900</v>
+        <v>5412500</v>
       </c>
       <c r="F60" s="3">
-        <v>5237800</v>
+        <v>5838400</v>
       </c>
       <c r="G60" s="3">
-        <v>4588100</v>
+        <v>6006000</v>
       </c>
       <c r="H60" s="3">
-        <v>4153100</v>
+        <v>5111600</v>
       </c>
       <c r="I60" s="3">
-        <v>4142600</v>
+        <v>4792300</v>
       </c>
       <c r="J60" s="3">
+        <v>4552000</v>
+      </c>
+      <c r="K60" s="3">
         <v>4524500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4077700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4666000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4599900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3985500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3039800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2502000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2503300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2386800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2208700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2015800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2192900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1619400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1539300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1370300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>923000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>972100</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5219,89 +5359,92 @@
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1119500</v>
+        <v>1325700</v>
       </c>
       <c r="E61" s="3">
-        <v>1088200</v>
+        <v>1122000</v>
       </c>
       <c r="F61" s="3">
-        <v>654100</v>
+        <v>1207200</v>
       </c>
       <c r="G61" s="3">
-        <v>490500</v>
+        <v>750000</v>
       </c>
       <c r="H61" s="3">
-        <v>454300</v>
+        <v>546500</v>
       </c>
       <c r="I61" s="3">
-        <v>478000</v>
+        <v>524200</v>
       </c>
       <c r="J61" s="3">
+        <v>525300</v>
+      </c>
+      <c r="K61" s="3">
         <v>490400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>638000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>680400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>630100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>906000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>860300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1044200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>560400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>549800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>582500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>241400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>397800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>315400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>462600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>531100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>295800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>367400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>381000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>481100</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5314,89 +5457,92 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>216400</v>
+        <v>129500</v>
       </c>
       <c r="E62" s="3">
-        <v>228400</v>
+        <v>106300</v>
       </c>
       <c r="F62" s="3">
-        <v>222100</v>
+        <v>141800</v>
       </c>
       <c r="G62" s="3">
-        <v>253000</v>
+        <v>142000</v>
       </c>
       <c r="H62" s="3">
-        <v>244800</v>
+        <v>180400</v>
       </c>
       <c r="I62" s="3">
-        <v>253900</v>
+        <v>177800</v>
       </c>
       <c r="J62" s="3">
+        <v>179000</v>
+      </c>
+      <c r="K62" s="3">
         <v>250300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>266800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3201800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>209800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>240400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>227700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>111300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>89400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>81800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>61100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>51000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18800</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,89 +5849,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6746400</v>
+        <v>6720900</v>
       </c>
       <c r="E66" s="3">
-        <v>6589000</v>
+        <v>6751400</v>
       </c>
       <c r="F66" s="3">
-        <v>6123600</v>
+        <v>7298900</v>
       </c>
       <c r="G66" s="3">
-        <v>5341600</v>
+        <v>7010600</v>
       </c>
       <c r="H66" s="3">
-        <v>4862200</v>
+        <v>5939900</v>
       </c>
       <c r="I66" s="3">
-        <v>4884500</v>
+        <v>5599000</v>
       </c>
       <c r="J66" s="3">
+        <v>5356300</v>
+      </c>
+      <c r="K66" s="3">
         <v>5275400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4997100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5399800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5528800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5764700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5090800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4210900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3163600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3160900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3048700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2519400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2442000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2518100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2102100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2090000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1681600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,89 +6375,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2897700</v>
+        <v>473400</v>
       </c>
       <c r="E72" s="3">
-        <v>2805200</v>
+        <v>367100</v>
       </c>
       <c r="F72" s="3">
-        <v>2736500</v>
+        <v>307400</v>
       </c>
       <c r="G72" s="3">
-        <v>2596800</v>
+        <v>240900</v>
       </c>
       <c r="H72" s="3">
-        <v>2515800</v>
+        <v>103600</v>
       </c>
       <c r="I72" s="3">
-        <v>2457500</v>
+        <v>22600</v>
       </c>
       <c r="J72" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="K72" s="3">
         <v>2407600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2430900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2614100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2732500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2954400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3096800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3211200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2986400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2794100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2861600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1274000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1250900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1116500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1055200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1034600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>998300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>918700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>132900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>175600</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,89 +6767,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2725400</v>
+        <v>2805200</v>
       </c>
       <c r="E76" s="3">
-        <v>2687300</v>
+        <v>2731400</v>
       </c>
       <c r="F76" s="3">
-        <v>2628100</v>
+        <v>2981100</v>
       </c>
       <c r="G76" s="3">
-        <v>2536600</v>
+        <v>3013500</v>
       </c>
       <c r="H76" s="3">
-        <v>2461900</v>
+        <v>2826000</v>
       </c>
       <c r="I76" s="3">
-        <v>2396600</v>
+        <v>2840900</v>
       </c>
       <c r="J76" s="3">
+        <v>2633400</v>
+      </c>
+      <c r="K76" s="3">
         <v>2317400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2343300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2519300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2659300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2732200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2907100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2918100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2969000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2778900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2839400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1249900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1227500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1103100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1040900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1019300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>986200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>908600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>126900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>167300</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>89200</v>
+        <v>99100</v>
       </c>
       <c r="E81" s="3">
-        <v>67000</v>
+        <v>89400</v>
       </c>
       <c r="F81" s="3">
-        <v>117100</v>
+        <v>74400</v>
       </c>
       <c r="G81" s="3">
-        <v>73500</v>
+        <v>134200</v>
       </c>
       <c r="H81" s="3">
-        <v>54900</v>
+        <v>81800</v>
       </c>
       <c r="I81" s="3">
-        <v>40700</v>
+        <v>63300</v>
       </c>
       <c r="J81" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K81" s="3">
         <v>14200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-97700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-62800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-160400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-252100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>102500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>58700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>48600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>40300</v>
+        <v>30200</v>
       </c>
       <c r="E83" s="3">
-        <v>39100</v>
+        <v>30500</v>
       </c>
       <c r="F83" s="3">
-        <v>39700</v>
+        <v>27000</v>
       </c>
       <c r="G83" s="3">
-        <v>40100</v>
+        <v>7600</v>
       </c>
       <c r="H83" s="3">
-        <v>39800</v>
+        <v>24300</v>
       </c>
       <c r="I83" s="3">
-        <v>38200</v>
+        <v>24500</v>
       </c>
       <c r="J83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K83" s="3">
         <v>38600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>37700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>22500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4400</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-128700</v>
+        <v>-24100</v>
       </c>
       <c r="E89" s="3">
-        <v>-444500</v>
+        <v>-129000</v>
       </c>
       <c r="F89" s="3">
-        <v>-74900</v>
+        <v>-493100</v>
       </c>
       <c r="G89" s="3">
-        <v>11400</v>
+        <v>-85900</v>
       </c>
       <c r="H89" s="3">
-        <v>149600</v>
+        <v>12700</v>
       </c>
       <c r="I89" s="3">
-        <v>210000</v>
+        <v>172700</v>
       </c>
       <c r="J89" s="3">
+        <v>230700</v>
+      </c>
+      <c r="K89" s="3">
         <v>61700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-31200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>143200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>159400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>120100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>358300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>256000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>45400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-326800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>219400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>71400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-122500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>35100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-353300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-55200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-344600</v>
+        <v>-31200</v>
       </c>
       <c r="E91" s="3">
-        <v>-306600</v>
+        <v>-37900</v>
       </c>
       <c r="F91" s="3">
-        <v>-285300</v>
+        <v>-36000</v>
       </c>
       <c r="G91" s="3">
-        <v>-176400</v>
+        <v>-29800</v>
       </c>
       <c r="H91" s="3">
-        <v>-332200</v>
+        <v>-11100</v>
       </c>
       <c r="I91" s="3">
-        <v>-416400</v>
+        <v>-40700</v>
       </c>
       <c r="J91" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-155300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-109300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-216800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-241800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-546400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-151300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-64800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-17800</v>
       </c>
       <c r="U91" s="3">
         <v>-17800</v>
       </c>
       <c r="V91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-104100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12000</v>
       </c>
-      <c r="E94" s="3">
-        <v>485300</v>
-      </c>
       <c r="F94" s="3">
-        <v>-306500</v>
+        <v>538400</v>
       </c>
       <c r="G94" s="3">
-        <v>236600</v>
+        <v>-351500</v>
       </c>
       <c r="H94" s="3">
-        <v>-91300</v>
+        <v>263600</v>
       </c>
       <c r="I94" s="3">
-        <v>9300</v>
+        <v>-105400</v>
       </c>
       <c r="J94" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-149700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-150500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-51200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-596400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>167200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-121200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>282300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>97400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-55100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>16900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>26700</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,31 +8352,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>93000</v>
+        <v>-10700</v>
       </c>
       <c r="E100" s="3">
-        <v>464500</v>
+        <v>93300</v>
       </c>
       <c r="F100" s="3">
-        <v>110000</v>
+        <v>515300</v>
       </c>
       <c r="G100" s="3">
-        <v>19900</v>
+        <v>126100</v>
       </c>
       <c r="H100" s="3">
-        <v>2800</v>
+        <v>22200</v>
       </c>
       <c r="I100" s="3">
-        <v>-159500</v>
+        <v>3200</v>
       </c>
       <c r="J100" s="3">
+        <v>-175200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-63100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-183300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-222700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-71400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>225100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-328900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>345300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>29800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>21700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1704200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-255100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-60000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>279100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>35200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>387000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>870200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>229100</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3600</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F101" s="3">
-        <v>-1200</v>
+        <v>2000</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
+        <v>2000</v>
       </c>
       <c r="H101" s="3">
-        <v>1300</v>
+        <v>-1100</v>
       </c>
       <c r="I101" s="3">
-        <v>1800</v>
+        <v>4600</v>
       </c>
       <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-500</v>
       </c>
       <c r="U101" s="3">
         <v>-500</v>
       </c>
       <c r="V101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-134100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-44100</v>
       </c>
-      <c r="E102" s="3">
-        <v>505400</v>
-      </c>
       <c r="F102" s="3">
-        <v>-272600</v>
+        <v>560600</v>
       </c>
       <c r="G102" s="3">
-        <v>267900</v>
+        <v>-312600</v>
       </c>
       <c r="H102" s="3">
-        <v>62400</v>
+        <v>298400</v>
       </c>
       <c r="I102" s="3">
-        <v>61600</v>
+        <v>72000</v>
       </c>
       <c r="J102" s="3">
+        <v>67700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-149300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-266700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-76700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-65300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>293400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-570100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>776300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-113000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>47600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-114400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>246200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>108400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>133600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-39500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>125900</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>564400</v>
+      </c>
+      <c r="E8" s="3">
         <v>590100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>556100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>587700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>638400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>591300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>572400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>504200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>545000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>463500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>461800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>414900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>641700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>296000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>118800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>168000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>185000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>182800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>130600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>141300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>144600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>124000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>110000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>100300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>94400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>76600</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>18900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E9" s="3">
         <v>157800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>151600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>161500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>165400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>154900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>142100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>142400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>125400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>124000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>125500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>135200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>130400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>105900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>58600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>46400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>38900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>23700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>422300</v>
+      </c>
+      <c r="E10" s="3">
         <v>432400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>404600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>426200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>473000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>436400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>430300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>361800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>419600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>339400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>336300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>279800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>511300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>190100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>121600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>145100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>142100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>91700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>111700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>120900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>103200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>91100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>84300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>76400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>61700</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3">
         <v>5200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,13 +1338,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>575300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1336,21 +1355,21 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-6000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1360,21 +1379,21 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1384,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1420,83 +1439,86 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E15" s="3">
         <v>33500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>32000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
         <v>3700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2500</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1506,8 +1528,8 @@
       <c r="AD15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>297400</v>
+      </c>
+      <c r="E17" s="3">
         <v>326400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>306700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>339900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>322700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>315700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>302300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>298400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>276800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>264600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>261400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>266200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>248200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>246300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>137800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>108700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>105800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>97300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>86800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>66800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>57700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>54800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>55900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>49000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>37000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="3">
         <v>36000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>28600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E18" s="3">
         <v>263700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>249400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>247800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>315800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>275500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>270100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>205900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>268200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>198900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>148700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>393500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>59300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>79200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>85600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>74400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>86900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>69100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>54100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>58300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>45400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>39700</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,187 +1815,191 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E20" s="3">
         <v>89100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>86000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>111100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>127500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>140900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>148300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>114500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-218400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-124900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-259800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-173000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-522600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-308900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>146700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-29500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>14400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>10500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E21" s="3">
         <v>208100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>193900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>168700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>221200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>179300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>167700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>133300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>88400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>111700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-106600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-216100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>146500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>66400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>82300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>84700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>43600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>56800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>77600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>59000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>45800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>51400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>37000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1973,65 +2009,68 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E22" s="3">
         <v>51600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>46000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>36200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>34200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>37500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>33800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>28400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2041,18 +2080,18 @@
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
@@ -2077,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-456500</v>
+      </c>
+      <c r="E23" s="3">
         <v>123000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>117400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>96500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>152100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>87600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-96900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-58100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-163600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-287600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>112800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>40700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>68900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>72700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>67000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>50600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>45800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>32000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>19900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E24" s="3">
         <v>23300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>5200</v>
       </c>
       <c r="AD24" s="3">
         <v>5200</v>
       </c>
       <c r="AE24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-472400</v>
+      </c>
+      <c r="E26" s="3">
         <v>99700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>89800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>135200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>82400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>63700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>44600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-98100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-62700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-161800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-253800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>101900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>57300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>48800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>48800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>32200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>16700</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-472800</v>
+      </c>
+      <c r="E27" s="3">
         <v>99100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>89400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>74400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>134200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>81800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>63300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>44800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-97700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-62800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-160400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-252100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>102500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>58700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>31300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>48600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>33100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>16400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-89100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-86000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-111100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-127500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-140900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-148300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-114500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>218400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>124900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>259800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>173000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>522600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>308900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-146700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>29500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>18200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>13400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15400</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-472800</v>
+      </c>
+      <c r="E33" s="3">
         <v>99100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>89400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>74400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>134200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>81800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>63300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>44800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-97700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-62800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-160400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-252100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>102500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>58700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>31300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>48600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>33100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-472800</v>
+      </c>
+      <c r="E35" s="3">
         <v>99100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>89400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>74400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>134200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>81800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>63300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>44800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-97700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-62800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-160400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-252100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>102500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>58700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>31300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>48600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>33100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,92 +3611,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>845200</v>
+      </c>
+      <c r="E41" s="3">
         <v>737000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>854400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>994600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>448500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>739500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>456800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>366500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>271900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>432900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>759000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>835700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>907400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>612600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1137100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>360800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>457800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>429000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>543400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>299300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>178900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>45300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>53200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>33400</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3624,92 +3710,95 @@
       <c r="AH41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E42" s="3">
         <v>68600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>717500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>409000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>724500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>643300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1332600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1069800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>498700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>505900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>402300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>452300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>968100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1679500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1520700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1601800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>154300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>474300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>542500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>522600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>507400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>497800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>494300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>26300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>48800</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3722,92 +3811,95 @@
       <c r="AH42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4938900</v>
+      </c>
+      <c r="E43" s="3">
         <v>5008400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5117400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5449000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5067800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4326600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3935400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3823300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3833700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3594600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3681400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3862800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4115000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4000100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3562700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3331500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3326300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3393000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2683200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2593100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2653500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2338800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2375200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1971100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3820,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3846,8 +3941,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3918,92 +4013,95 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1563900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1530100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1366600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1426800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1422900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>993200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>952300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>881200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>75900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>659900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>591100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>619300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>443700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>248600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>206600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>172200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>123600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>28000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4016,92 +4114,95 @@
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7431800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7344100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7357600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7962900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7656700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6492300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6095400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5740600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5510400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5173200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5598900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5795500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6044000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5508700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5916500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5578400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5477000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5547500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3463800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3417800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3399400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2934700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2921800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2492300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4114,92 +4215,95 @@
       <c r="AH46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E47" s="3">
         <v>20500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>76600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>91100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>75400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>209000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>276400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>435900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>694500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>81200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>82600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4212,92 +4316,95 @@
       <c r="AH47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E48" s="3">
         <v>327200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>315700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>344300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>348900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>338200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>360400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>356600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>295000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>303500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>336800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>329100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>316800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>262100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>188200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>172800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>134200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>126500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>117700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>117200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>101300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>88500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>70500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>62800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>47500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>46800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>57400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4310,92 +4417,95 @@
       <c r="AH48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>874300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1640200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1599600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1747200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1806100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1742000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1796000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1700900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1551500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1588700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1721100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1692800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1673300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1655300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>220700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>205200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>194600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>151500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>135900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>69000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>67800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>60700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>58500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>54900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>56800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>55900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4408,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,92 +4720,95 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E52" s="3">
         <v>26700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>159300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>183800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>186900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>161700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>189000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>135800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>109100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>95100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>51500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>50200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>46400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>49600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>43900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>46600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>51200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>51900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>48400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>46800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>54500</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4702,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,92 +4922,95 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8862500</v>
+      </c>
+      <c r="E54" s="3">
         <v>9536000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9492700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10290600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10035200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8777000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8451500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8000700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7592800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7340400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7919100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8188100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8496900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7997900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7129000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6132700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5939900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5888100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3769200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3669500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3621200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3143000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3109300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2667700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4898,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,92 +5099,93 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E57" s="3">
         <v>103600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>94700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>101800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>90100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>87800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>98100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3086800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2812000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>79300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3075300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3248800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2991400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2156500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1673900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1749800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1691700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1382700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1118700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1218600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1073100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1105200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1088800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>912300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>865300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>940200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5068,92 +5198,95 @@
       <c r="AH57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>803500</v>
+      </c>
+      <c r="E58" s="3">
         <v>517300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>547200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>444900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>387400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>394300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>396000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>381200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>507300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>462000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>681200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>889600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>781800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>572100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>672500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>656700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>588400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>570000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>739900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>839400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>930600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>512800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>398400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>246700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>138700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3900</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5166,92 +5299,95 @@
       <c r="AH58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4398600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4423800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4679800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5212600</v>
       </c>
-      <c r="G59" s="3">
-        <v>5388600</v>
-      </c>
       <c r="H59" s="3">
+        <v>5324400</v>
+      </c>
+      <c r="I59" s="3">
         <v>4516500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4211500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3994000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>930400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>803600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>740000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>701100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>569300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>422000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>210700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>171300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>165100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>125200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>86200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>57700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>43600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>33500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>34700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>29100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>46900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>27900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5264,92 +5400,95 @@
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5421900</v>
+      </c>
+      <c r="E60" s="3">
         <v>5155500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5412500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5838400</v>
       </c>
-      <c r="G60" s="3">
-        <v>6006000</v>
-      </c>
       <c r="H60" s="3">
+        <v>5941700</v>
+      </c>
+      <c r="I60" s="3">
         <v>5111600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4792300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4552000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4524500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4077700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1500500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4666000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4599900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3985500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3039800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2502000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2503300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2386800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2208700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2015800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2192900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1619400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1539300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1370300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>923000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>972100</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5362,92 +5501,95 @@
       <c r="AH60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1281500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1325700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1122000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1207200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>750000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>546500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>524200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>525300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>490400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>638000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>680400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>630100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>906000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>860300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1044200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>560400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>549800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>582500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>241400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>397800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>315400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>462600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>531100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>295800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>367400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>381000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>481100</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5460,92 +5602,95 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E62" s="3">
         <v>129500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>141800</v>
       </c>
-      <c r="G62" s="3">
-        <v>142000</v>
-      </c>
       <c r="H62" s="3">
+        <v>206200</v>
+      </c>
+      <c r="I62" s="3">
         <v>180400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>177800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>179000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>250300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>266800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3201800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>209800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>240400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>227700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>111300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>89400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>81800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>61100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>51000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>20200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18800</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5558,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,92 +6006,95 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6950200</v>
+      </c>
+      <c r="E66" s="3">
         <v>6720900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6751400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7298900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7010600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5939900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5599000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5356300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5275400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4997100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5399800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5528800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5764700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5090800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4210900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3163600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3160900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3048700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2519400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2442000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2518100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2102100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2090000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1681600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5950,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,92 +6548,95 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E72" s="3">
         <v>473400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>367100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>307400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>240900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>103600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-38800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2407600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2430900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2614100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2732500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2954400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3096800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3211200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2986400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2794100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2861600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1274000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1250900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1116500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1055200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1034600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>998300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>918700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>132900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>175600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6476,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,92 +6952,95 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1904000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2805200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2731400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2981100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3013500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2826000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2840900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2633400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2317400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2343300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2519300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2659300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2732200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2907100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2918100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2969000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2778900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2839400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1249900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1227500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1103100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1040900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1019300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>986200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>908600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>126900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>167300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6868,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-472800</v>
+      </c>
+      <c r="E81" s="3">
         <v>99100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>89400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>74400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>134200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>81800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>63300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>44800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-97700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-62800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-160400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-252100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>102500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>58700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>31300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>48600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>33100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E83" s="3">
         <v>30200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>39500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>22500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4400</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-129000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-493100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-85900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>172700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>230700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-31200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>143200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>159400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>120100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>358300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>256000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-326800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>219400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>71400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-122500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-353300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-55200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-29800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-50100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-11100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-67200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-155300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-109300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-216800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-241800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-546400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-151300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-64800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-17800</v>
       </c>
       <c r="V91" s="3">
         <v>-17800</v>
       </c>
       <c r="W91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-77500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-104100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>538400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-351500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>263600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-105400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-149700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-51100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-150500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-51200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-596400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>167200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-121200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>282300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>97400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-55100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>16900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>4300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>26700</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8379,8 +8612,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>322800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>93300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>515300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>126100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>22200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-175200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-63100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-183300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-222700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-71400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>225100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-328900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>345300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>29800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1704200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-255100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-60000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>279100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>35200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>387000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>870200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>229100</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1500</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2000</v>
       </c>
       <c r="G101" s="3">
         <v>2000</v>
       </c>
       <c r="H101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-500</v>
       </c>
       <c r="V101" s="3">
         <v>-500</v>
       </c>
       <c r="W101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>196300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-134100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-44100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>560600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-312600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>298400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>67700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-149300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-266700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-76700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-65300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>293400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-570100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>776300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-113000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>47600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-114400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>246200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>108400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>133600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-39500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>125900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>607100</v>
+      </c>
+      <c r="E8" s="3">
         <v>564400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>590100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>556100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>587700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>638400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>591300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>572400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>504200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>545000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>463500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>461800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>414900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>641700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>296000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>118800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>168000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>185000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>182800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>130600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>141300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>144600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>124000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>110000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>100300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>94400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>76600</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>18900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E9" s="3">
         <v>142100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>157800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>151600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>161500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>165400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>154900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>142100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>142400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>125400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>124000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>125500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>135200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>130400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>105900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>58600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>38900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>444200</v>
+      </c>
+      <c r="E10" s="3">
         <v>422300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>432400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>404600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>426200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>473000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>436400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>430300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>361800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>419600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>339400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>336300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>279800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>511300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>190100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>60200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>121600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>145100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>142100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>91700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>111700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>120900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>103200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>91100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>84300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>76400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>61700</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3">
         <v>5200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,38 +1358,41 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>575300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-6000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1382,21 +1402,21 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1406,8 +1426,8 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1442,86 +1462,89 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E15" s="3">
         <v>29400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30500</v>
       </c>
-      <c r="G15" s="3">
-        <v>32000</v>
-      </c>
       <c r="H15" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I15" s="3">
         <v>32900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>46000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>27400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4000</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>3700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2500</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1531,8 +1554,8 @@
       <c r="AE15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E17" s="3">
         <v>297400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>326400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>306700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>339900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>322700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>315700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>302300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>298400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>276800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>264600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>261400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>266200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>248200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>246300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>137800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>108700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>105800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>97300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>86800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>66800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>57700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>54800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>55900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>42000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>49000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>37000</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="3">
         <v>36000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>28600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>269400</v>
+      </c>
+      <c r="E18" s="3">
         <v>267000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>263700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>249400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>247800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>315800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>275500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>270100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>205900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>268200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>198900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>148700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>393500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>49700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>59300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>79200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>85600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>74400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>86900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>69100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>54100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>58300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>45400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>39700</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,193 +1849,197 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E20" s="3">
         <v>96700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>89100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>86000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>111100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>127500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>140900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>148300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>114500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-218400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-124900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-259800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-173000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-522600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-308900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>146700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-29500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>14400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E21" s="3">
         <v>199600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>208100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>193900</v>
       </c>
-      <c r="G21" s="3">
-        <v>168700</v>
-      </c>
       <c r="H21" s="3">
+        <v>168900</v>
+      </c>
+      <c r="I21" s="3">
         <v>221200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>179300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>167700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>133300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>111700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-106600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-216100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>146500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>66400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>82300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>84700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>56800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>59000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>51400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>37000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28700</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2012,68 +2049,71 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3">
         <v>6900</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E22" s="3">
         <v>51500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>51600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>46000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>37500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>33800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>34500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>28400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2083,18 +2123,18 @@
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-456500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>123000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>117400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>152100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>100800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>87600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-96900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-58100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-163600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-287600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>112800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>40700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>68900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>72700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>67000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>50600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>39200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>45800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>32000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E24" s="3">
         <v>15900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>23900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-33700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>23900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>5200</v>
       </c>
       <c r="AE24" s="3">
         <v>5200</v>
       </c>
       <c r="AF24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-472400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>99700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>89800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>74500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>135200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>63700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-62700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-161800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-253800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>101900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>57300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>48800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>48800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>35300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>32200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>33100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>22700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>16700</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-472800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>99100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>89400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>74400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>134200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>81800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>63300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-97700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-62800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-160400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-252100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>102500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>58700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>49900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>31300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>48600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>22700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>16400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-96700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-89100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-86000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-111100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-127500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-140900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-148300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-114500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>218400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>124900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>259800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>173000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>522600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>308900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-146700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>29500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>18200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>14800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>12500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15400</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-472800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>99100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>89400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>74400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>134200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>81800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>63300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>44800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-97700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-62800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-160400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-252100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>102500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>58700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>49900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>31300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>48600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-472800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>99100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>89400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>74400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>134200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>81800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>63300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>44800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-97700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-62800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-160400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-252100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>102500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>58700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>49900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>31300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>48600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>985500</v>
+      </c>
+      <c r="E41" s="3">
         <v>845200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>737000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>854400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>994600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>448500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>739500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>456800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>366500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>271900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>432900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>759000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>835700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>907400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>612600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1137100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>360800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>457800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>429000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>543400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>299300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>178900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>45300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>53200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>33400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3713,95 +3800,98 @@
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E42" s="3">
         <v>83700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>68600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>717500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>409000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>724500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>643300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1332600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1069800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>498700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>505900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>402300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>452300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>968100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1679500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1520700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1601800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>154300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>474300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>542500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>522600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>507400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>497800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>494300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>26300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>48800</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3814,95 +3904,98 @@
       <c r="AI42" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6296100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4938900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5008400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5117400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5449000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5067800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4326600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3935400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3823300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3833700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3594600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3681400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3862800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4115000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4000100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3562700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3331500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3326300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3393000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2683200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2593100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2653500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2338800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2375200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1971100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3915,8 +4008,11 @@
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3944,8 +4040,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4016,95 +4112,98 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>528500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1563900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1530100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1366600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1426800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1422900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>993200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>952300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>881200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>72200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>75900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>659900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>591100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>619300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>443700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>248600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>206600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>172200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>123600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>28000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4117,95 +4216,98 @@
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7835600</v>
+      </c>
+      <c r="E46" s="3">
         <v>7431800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7344100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7357600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7962900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7656700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6492300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6095400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5740600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5510400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5173200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5598900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5795500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6044000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5508700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5916500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5578400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5477000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5547500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3463800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3417800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3399400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2934700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2921800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2492300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4218,95 +4320,98 @@
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E47" s="3">
         <v>17500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>76600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>91100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>75400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>209000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>276400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>435900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>694500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>81200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>82600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4319,95 +4424,98 @@
       <c r="AI47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>335700</v>
+      </c>
+      <c r="E48" s="3">
         <v>304800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>327200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>315700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>344300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>348900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>338200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>360400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>356600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>295000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>303500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>336800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>329100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>316800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>262100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>188200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>134200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>126500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>117700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>101300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>88500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>70500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>62800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>47500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>46800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>57400</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4420,95 +4528,98 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>948300</v>
+      </c>
+      <c r="E49" s="3">
         <v>874300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1640200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1599600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1747200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1806100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1742000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1796000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1700900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1551500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1588700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1721100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1692800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1673300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1655300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>220700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>205200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>194600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>151500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>135900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>75200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>69000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>67800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>60700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>58500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>54900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>56800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>55900</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,95 +4840,98 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E52" s="3">
         <v>42400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>159300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>183800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>186900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>161700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>189000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>135800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>109100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>95100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>51500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>50200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>46400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>49600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>46600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>51200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>51900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>48400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>46800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>54500</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,95 +5048,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9406800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8862500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9536000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9492700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10290600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10035200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8777000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8451500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8000700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7592800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7340400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7919100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8188100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8496900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7997900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7129000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6132700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5939900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5888100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3769200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3669500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3621200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3143000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3109300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2667700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,95 +5230,96 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E57" s="3">
         <v>108700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>103600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>94700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>105900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>90100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>87800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>98100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3086800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2812000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>79300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3075300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3248800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2991400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2156500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1673900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1749800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1691700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1382700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1118700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1218600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1073100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1105200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1088800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>912300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>865300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>940200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5201,95 +5332,98 @@
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>861400</v>
+      </c>
+      <c r="E58" s="3">
         <v>803500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>517300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>547200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>444900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>387400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>394300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>396000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>381200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>507300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>462000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>681200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>889600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>781800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>572100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>672500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>656700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>588400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>570000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>739900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>839400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>930600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>512800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>398400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>246700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>138700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3900</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5302,95 +5436,98 @@
       <c r="AI58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4575900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4398600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4423800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4679800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5212600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5324400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4516500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4211500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3994000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>930400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>803600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>740000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>701100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>569300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>422000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>210700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>171300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>165100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>125200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>86200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>57700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>43600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>33500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>35700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>34700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>29100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>46900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5403,95 +5540,98 @@
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5637000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5421900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5155500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5412500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5838400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5941700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5111600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4792300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4552000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4524500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4077700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1500500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4666000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4599900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3985500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3039800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2502000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2503300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2386800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2208700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2015800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2192900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1619400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1539300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1370300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>923000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>972100</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5504,95 +5644,98 @@
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1481900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1281500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1325700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1122000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1207200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>750000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>546500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>524200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>525300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>490400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>638000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>680400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>630100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>906000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>860300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1044200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>560400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>549800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>582500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>241400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>397800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>315400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>462600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>531100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>295800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>367400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>381000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>481100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5605,95 +5748,98 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>150700</v>
+      </c>
+      <c r="E62" s="3">
         <v>136700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>129500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>106300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>141800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>206200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>180400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>177800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>179000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>250300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>266800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3201800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>209800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>240400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>227700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>111300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>89400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>81800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>61100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>51000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>20200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>19700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18800</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,95 +6164,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7406800</v>
+      </c>
+      <c r="E66" s="3">
         <v>6950200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6720900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6751400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7298900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7010600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5939900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5599000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5356300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5275400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4997100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5399800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5528800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5764700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5090800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4210900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3163600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3160900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3048700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2519400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2442000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2518100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2102100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2090000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1681600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,95 +6722,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-56000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>473400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>367100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>307400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>240900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>103600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-38800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2407600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2430900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2614100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2732500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2954400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3096800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3211200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2986400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2794100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2861600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1274000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1250900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1116500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1055200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1034600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>998300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>918700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>132900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>175600</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,95 +7138,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1991200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1904000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2805200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2731400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2981100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3013500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2826000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2840900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2633400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2317400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2343300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2519300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2659300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2732200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2907100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2918100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2969000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2778900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2839400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1249900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1227500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1103100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1040900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1019300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>986200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>908600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>126900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>167300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-472800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>99100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>89400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>74400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>134200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>81800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>63300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>44800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-97700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-62800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-160400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-252100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>102500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>58700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>49900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>31300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>48600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>39500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4400</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-48600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-129000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-493100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-85900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>172700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>230700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>61700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-31200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>143200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>159400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>120100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>358300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>256000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>45400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-326800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>219400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>71400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-122500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-353300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-55200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-69100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-50100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-155300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-109300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-216800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-241800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-546400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-151300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-36800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-64800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-17800</v>
       </c>
       <c r="W91" s="3">
         <v>-17800</v>
       </c>
       <c r="X91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-104100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>538400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-351500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>263600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-105400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-149700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-51100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-150500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-596400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>167200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-121200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>282300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>97400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-55100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>16900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>4300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>26700</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8615,8 +8849,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E100" s="3">
         <v>322800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>93300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>515300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>126100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-175200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-63100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-183300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-222700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-71400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>225100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-328900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>345300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>29800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1704200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-255100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-60000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>279100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>35200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>387000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>870200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>229100</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2000</v>
       </c>
       <c r="H101" s="3">
         <v>2000</v>
       </c>
       <c r="I101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-500</v>
       </c>
       <c r="W101" s="3">
         <v>-500</v>
       </c>
       <c r="X101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E102" s="3">
         <v>196300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-134100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-44100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>560600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-312600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>298400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>72000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>67700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-149300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-266700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-76700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-65300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>293400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-570100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>776300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-113000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>47600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-114400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>246200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>108400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>133600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-39500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>125900</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>607100</v>
+        <v>603100</v>
       </c>
       <c r="E8" s="3">
+        <v>554600</v>
+      </c>
+      <c r="F8" s="3">
         <v>564400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>590100</v>
       </c>
-      <c r="G8" s="3">
-        <v>556100</v>
-      </c>
       <c r="H8" s="3">
-        <v>587700</v>
+        <v>503600</v>
       </c>
       <c r="I8" s="3">
+        <v>527400</v>
+      </c>
+      <c r="J8" s="3">
         <v>638400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>591300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>572400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>504200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>545000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>463500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>461800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>414900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>641700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>296000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>118800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>168000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>185000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>182800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>130600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>141300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>144600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>124000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>110000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>100300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>94400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>76600</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>18900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>162900</v>
+        <v>156100</v>
       </c>
       <c r="E9" s="3">
+        <v>137100</v>
+      </c>
+      <c r="F9" s="3">
         <v>142100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>157800</v>
       </c>
-      <c r="G9" s="3">
-        <v>151600</v>
-      </c>
       <c r="H9" s="3">
-        <v>161500</v>
+        <v>125600</v>
       </c>
       <c r="I9" s="3">
+        <v>132300</v>
+      </c>
+      <c r="J9" s="3">
         <v>165400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>154900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>142100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>142400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>125400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>124000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>125500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>135200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>130400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>105900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>46400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>38900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>29500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>18800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>13800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>444200</v>
+        <v>447000</v>
       </c>
       <c r="E10" s="3">
+        <v>417500</v>
+      </c>
+      <c r="F10" s="3">
         <v>422300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>432400</v>
       </c>
-      <c r="G10" s="3">
-        <v>404600</v>
-      </c>
       <c r="H10" s="3">
-        <v>426200</v>
+        <v>378000</v>
       </c>
       <c r="I10" s="3">
+        <v>395100</v>
+      </c>
+      <c r="J10" s="3">
         <v>473000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>436400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>430300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>361800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>419600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>339400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>336300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>279800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>511300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>190100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>121600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>145100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>142100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>91700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>111700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>120900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>103200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>91100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>84300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>76400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>61700</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3">
         <v>5200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,41 +1378,44 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>575300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-6000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1405,21 +1425,21 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>2200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1429,8 +1449,8 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1465,89 +1485,92 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E15" s="3">
         <v>32700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33500</v>
       </c>
-      <c r="G15" s="3">
-        <v>30500</v>
-      </c>
       <c r="H15" s="3">
+        <v>30300</v>
+      </c>
+      <c r="I15" s="3">
         <v>32200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>46000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>42000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>27400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
         <v>3700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2500</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1557,8 +1580,8 @@
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>337700</v>
+        <v>315200</v>
       </c>
       <c r="E17" s="3">
+        <v>287100</v>
+      </c>
+      <c r="F17" s="3">
         <v>297400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>326400</v>
       </c>
-      <c r="G17" s="3">
-        <v>306700</v>
-      </c>
       <c r="H17" s="3">
-        <v>339900</v>
+        <v>257100</v>
       </c>
       <c r="I17" s="3">
+        <v>287600</v>
+      </c>
+      <c r="J17" s="3">
         <v>322700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>315700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>302300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>298400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>276800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>264600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>261400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>266200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>248200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>246300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>137800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>108700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>105800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>97300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>86800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>66800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>57700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>54800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>55900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>42000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>49000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>37000</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI17" s="3">
         <v>36000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>269400</v>
+        <v>287900</v>
       </c>
       <c r="E18" s="3">
+        <v>267500</v>
+      </c>
+      <c r="F18" s="3">
         <v>267000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>263700</v>
       </c>
-      <c r="G18" s="3">
-        <v>249400</v>
-      </c>
       <c r="H18" s="3">
-        <v>247800</v>
+        <v>246400</v>
       </c>
       <c r="I18" s="3">
+        <v>239800</v>
+      </c>
+      <c r="J18" s="3">
         <v>315800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>275500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>270100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>205900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>268200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>198900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>148700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>393500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>79200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>85600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>43800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>74400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>86900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>69100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>54100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>58300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>45400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>39700</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,199 +1883,203 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>90400</v>
+        <v>78400</v>
       </c>
       <c r="E20" s="3">
+        <v>90200</v>
+      </c>
+      <c r="F20" s="3">
         <v>96700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>89100</v>
       </c>
-      <c r="G20" s="3">
-        <v>86000</v>
-      </c>
       <c r="H20" s="3">
-        <v>111100</v>
+        <v>85100</v>
       </c>
       <c r="I20" s="3">
+        <v>144100</v>
+      </c>
+      <c r="J20" s="3">
         <v>127500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>140900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>148300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>114500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-218400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-124900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-259800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-522600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-308900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>146700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-14800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>14400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>211700</v>
+        <v>244400</v>
       </c>
       <c r="E21" s="3">
+        <v>209900</v>
+      </c>
+      <c r="F21" s="3">
         <v>199600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>208100</v>
       </c>
-      <c r="G21" s="3">
-        <v>193900</v>
-      </c>
       <c r="H21" s="3">
-        <v>168900</v>
+        <v>191600</v>
       </c>
       <c r="I21" s="3">
+        <v>127800</v>
+      </c>
+      <c r="J21" s="3">
         <v>221200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>179300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>167700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>133300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>88400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>111700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-19900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-106600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-216100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>146500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>66400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>82300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>84700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>56800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>77600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>59000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>45800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>51400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>28700</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2052,71 +2089,74 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>67800</v>
+        <v>82600</v>
       </c>
       <c r="E22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="F22" s="3">
         <v>51500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>51600</v>
       </c>
-      <c r="G22" s="3">
-        <v>46000</v>
-      </c>
       <c r="H22" s="3">
-        <v>40200</v>
+        <v>45800</v>
       </c>
       <c r="I22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J22" s="3">
         <v>36200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>36800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>37500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>33800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>34500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2126,18 +2166,18 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>111200</v>
+        <v>126900</v>
       </c>
       <c r="E23" s="3">
+        <v>109500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-456500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>123000</v>
       </c>
-      <c r="G23" s="3">
-        <v>117400</v>
-      </c>
       <c r="H23" s="3">
-        <v>96500</v>
+        <v>115500</v>
       </c>
       <c r="I23" s="3">
+        <v>90000</v>
+      </c>
+      <c r="J23" s="3">
         <v>152100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>87600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>60600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-96900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-163600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-287600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>112800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>40700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>68900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>72700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>31300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>67000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>50600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>39200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>45800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>32000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>21100</v>
+        <v>19100</v>
       </c>
       <c r="E24" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F24" s="3">
         <v>15900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>23300</v>
       </c>
-      <c r="G24" s="3">
-        <v>27600</v>
-      </c>
       <c r="H24" s="3">
-        <v>22000</v>
+        <v>25500</v>
       </c>
       <c r="I24" s="3">
+        <v>20300</v>
+      </c>
+      <c r="J24" s="3">
         <v>16900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-33700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>23900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>5200</v>
       </c>
       <c r="AF24" s="3">
         <v>5200</v>
       </c>
       <c r="AG24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>90100</v>
+        <v>107800</v>
       </c>
       <c r="E26" s="3">
+        <v>89200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-472400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>99700</v>
       </c>
-      <c r="G26" s="3">
-        <v>89800</v>
-      </c>
       <c r="H26" s="3">
-        <v>74500</v>
+        <v>89900</v>
       </c>
       <c r="I26" s="3">
+        <v>69700</v>
+      </c>
+      <c r="J26" s="3">
         <v>135200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-98100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-62700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-161800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-253800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>101900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>57300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>48800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>48800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>35300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>32200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>33100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16700</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>89700</v>
+        <v>110700</v>
       </c>
       <c r="E27" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-472800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>99100</v>
       </c>
-      <c r="G27" s="3">
-        <v>89400</v>
-      </c>
       <c r="H27" s="3">
-        <v>74400</v>
+        <v>89800</v>
       </c>
       <c r="I27" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J27" s="3">
         <v>134200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>63300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>44800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-97700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-62800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-160400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-252100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>102500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>58700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>49900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>31300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>48600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>32300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>33100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>22700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,16 +2844,19 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2804,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-90400</v>
+        <v>-78400</v>
       </c>
       <c r="E32" s="3">
+        <v>-90200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-96700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-89100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-86000</v>
-      </c>
       <c r="H32" s="3">
-        <v>-111100</v>
+        <v>-85100</v>
       </c>
       <c r="I32" s="3">
+        <v>-144100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-127500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-140900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-148300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-114500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>218400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>124900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>259800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>173000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>522600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>308900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-146700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>29500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>19600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>18200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>14800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>13400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15400</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>89700</v>
+        <v>110700</v>
       </c>
       <c r="E33" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-472800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>99100</v>
       </c>
-      <c r="G33" s="3">
-        <v>89400</v>
-      </c>
       <c r="H33" s="3">
-        <v>74400</v>
+        <v>89800</v>
       </c>
       <c r="I33" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J33" s="3">
         <v>134200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>63300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>44800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-97700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-62800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-160400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-252100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>102500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>58700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>49900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>48600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>32300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>89700</v>
+        <v>110700</v>
       </c>
       <c r="E35" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-472800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>99100</v>
       </c>
-      <c r="G35" s="3">
-        <v>89400</v>
-      </c>
       <c r="H35" s="3">
-        <v>74400</v>
+        <v>89800</v>
       </c>
       <c r="I35" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J35" s="3">
         <v>134200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>63300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>44800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-97700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-62800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-160400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-252100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>102500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>58700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>49900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>48600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>32300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,98 +3785,99 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>951700</v>
+      </c>
+      <c r="E41" s="3">
         <v>985500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>845200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>737000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>854400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>994600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>448500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>739500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>456800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>366500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>271900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>432900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>759000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>835700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>907400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>612600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1137100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>360800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>457800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>429000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>543400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>299300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>178900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>45300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>53200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33400</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3803,98 +3890,101 @@
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E42" s="3">
         <v>25500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>83700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>68600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>717500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>409000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>724500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>643300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1332600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1069800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>498700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>505900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>402300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>452300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>968100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1679500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1520700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1601800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>154300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>474300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>542500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>522600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>507400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>497800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>494300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>26300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>48800</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3907,98 +3997,101 @@
       <c r="AJ42" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6872500</v>
+      </c>
+      <c r="E43" s="3">
         <v>6296100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4938900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5008400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5117400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5449000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5067800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4326600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3935400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3823300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3833700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3594600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3681400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3862800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4115000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4000100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3562700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3331500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3326300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3393000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2683200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2593100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2653500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2338800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2375200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1971100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4011,8 +4104,11 @@
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4043,8 +4139,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4115,98 +4211,101 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1250800</v>
+      </c>
+      <c r="E45" s="3">
         <v>528500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1563900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1530100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1366600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1426800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1422900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>993200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>952300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>881200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>72200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>75900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>659900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>591100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>619300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>443700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>248600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>206600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>172200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>123600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>82800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>28000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,98 +4318,101 @@
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9118000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7835600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7431800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7344100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7357600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7962900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7656700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6492300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6095400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5740600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5510400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5173200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5598900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5795500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6044000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5508700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5916500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5578400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5477000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5547500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3463800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3417800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3399400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2934700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2921800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2492300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4323,98 +4425,101 @@
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E47" s="3">
         <v>19200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>32300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>76600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>91100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>75400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>209000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>276400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>435900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>694500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>81200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>82600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4427,98 +4532,101 @@
       <c r="AJ47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>341700</v>
+      </c>
+      <c r="E48" s="3">
         <v>335700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>304800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>327200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>315700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>344300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>348900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>338200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>360400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>356600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>295000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>303500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>336800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>329100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>316800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>262100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>188200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>172800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>134200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>126500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>117200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>101300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>88500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>70500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>62800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>47500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>46800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>57400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4531,98 +4639,101 @@
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E49" s="3">
         <v>948300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>874300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1640200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1599600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1747200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1806100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1742000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1796000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1700900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1551500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1588700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1721100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1692800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1673300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1655300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>220700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>205200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>194600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>151500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>135900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>75200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>69000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>67800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>60700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>58500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>54900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>56800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>55900</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,98 +4960,101 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E52" s="3">
         <v>27400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>159300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>183800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>186900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>161700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>189000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>135800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>109100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>95100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>51500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>50200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>49600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>46600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>51200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>51900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>48400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>46800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>54500</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,98 +5174,101 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10122500</v>
+      </c>
+      <c r="E54" s="3">
         <v>9406800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8862500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9536000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9492700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10290600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10035200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8777000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8451500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8000700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7592800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7340400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7919100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8188100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8496900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7997900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7129000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6132700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5939900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5888100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3769200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3669500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3621200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3143000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3109300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2667700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,98 +5361,99 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E57" s="3">
         <v>125900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>108700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>103600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>94700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>105900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>90100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>87800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>98100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3086800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2812000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>79300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3075300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3248800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2991400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2156500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1673900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1749800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1691700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1382700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1118700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1218600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1073100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1105200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1088800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>912300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>865300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>940200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5335,98 +5466,101 @@
       <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>938900</v>
+      </c>
+      <c r="E58" s="3">
         <v>861400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>803500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>517300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>547200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>444900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>387400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>394300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>396000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>381200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>507300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>462000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>681200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>889600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>781800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>572100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>672500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>656700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>588400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>570000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>739900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>839400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>930600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>512800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>398400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>246700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>138700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3900</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5439,98 +5573,101 @@
       <c r="AJ58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5036200</v>
+      </c>
+      <c r="E59" s="3">
         <v>4575900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4398600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4423800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4679800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5212600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5324400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4516500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4211500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3994000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>930400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>803600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>740000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>701100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>569300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>422000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>210700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>171300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>165100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>125200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>86200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>57700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>43600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>34700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>29100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>46900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>27900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5543,98 +5680,101 @@
       <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6181600</v>
+      </c>
+      <c r="E60" s="3">
         <v>5637000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5421900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5155500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5412500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5838400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5941700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5111600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4792300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4552000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4524500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4077700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1500500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4666000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4599900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3985500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3039800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2502000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2503300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2386800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2208700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2015800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2192900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1619400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1539300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1370300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>923000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>972100</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5647,98 +5787,101 @@
       <c r="AJ60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1622400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1481900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1281500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1325700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1122000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1207200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>750000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>546500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>524200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>525300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>490400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>638000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>680400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>630100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>906000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>860300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1044200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>560400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>549800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>582500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>241400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>397800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>315400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>462600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>531100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>295800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>367400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>381000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>481100</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5751,98 +5894,101 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E62" s="3">
         <v>150700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>136700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>129500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>106300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>141800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>206200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>180400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>177800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>179000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>250300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>266800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3201800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>209800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>240400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>227700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>111300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>89400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>81800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>61100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>51000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>15400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>18800</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,98 +6322,101 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7990100</v>
+      </c>
+      <c r="E66" s="3">
         <v>7406800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6950200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6720900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6751400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7298900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7010600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5939900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5599000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5356300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5275400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4997100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5399800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5528800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5764700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5090800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4210900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3163600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3160900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3048700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2519400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2442000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2518100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2102100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2090000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1681600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,98 +6896,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E72" s="3">
         <v>29300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-56000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>473400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>367100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>307400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>240900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>103600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-38800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2407600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2430900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2614100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2732500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2954400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3096800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3211200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2986400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2794100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2861600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1274000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1250900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1116500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1055200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1034600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>998300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>918700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>132900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>175600</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,98 +7324,101 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2122800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1991200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1904000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2805200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2731400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2981100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3013500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2826000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2840900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2633400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2317400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2343300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2519300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2659300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2732200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2907100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2918100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2969000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2778900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2839400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1249900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1227500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1103100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1040900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1019300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>986200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>908600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>126900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>167300</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>89700</v>
+        <v>110700</v>
       </c>
       <c r="E81" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-472800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>99100</v>
       </c>
-      <c r="G81" s="3">
-        <v>89400</v>
-      </c>
       <c r="H81" s="3">
-        <v>74400</v>
+        <v>89800</v>
       </c>
       <c r="I81" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J81" s="3">
         <v>134200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>63300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>44800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-97700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-62800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-160400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-252100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>102500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>58700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>49900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>48600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>32300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7798,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E83" s="3">
         <v>32000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>39500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>43100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4400</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E89" s="3">
         <v>108900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-48600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-129000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-493100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-85900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>172700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>230700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>61700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-31200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>143200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>159400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>120100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>358300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>256000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>45400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-326800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>219400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>71400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-122500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-353300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-55200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-37900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-50100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-155300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-109300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-216800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-241800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-546400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-151300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-64800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-17800</v>
       </c>
       <c r="X91" s="3">
         <v>-17800</v>
       </c>
       <c r="Y91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-73200</v>
+      </c>
+      <c r="E94" s="3">
         <v>13800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-104100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>538400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-351500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>263600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-105400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-149700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-51100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-150500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-596400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>167200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-121200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>282300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>97400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>16900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>4300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>26700</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8852,8 +9086,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-46800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>322800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>93300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>515300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>126100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-175200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-63100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-183300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-222700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>225100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-328900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>345300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>29800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1704200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-255100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>279100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>35200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>387000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>870200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>229100</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1500</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2000</v>
       </c>
       <c r="I101" s="3">
         <v>2000</v>
       </c>
       <c r="J101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-500</v>
       </c>
       <c r="X101" s="3">
         <v>-500</v>
       </c>
       <c r="Y101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>73700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>196300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-134100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-44100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>560600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-312600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>298400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>72000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>67700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-149300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-266700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-76700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>293400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-570100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>776300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-113000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>47600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-114400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>246200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>108400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>133600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>15600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-39500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>125900</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>642600</v>
+      </c>
+      <c r="E8" s="3">
         <v>636900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>603100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>554600</v>
       </c>
-      <c r="G8" s="3">
-        <v>564400</v>
-      </c>
       <c r="H8" s="3">
+        <v>514800</v>
+      </c>
+      <c r="I8" s="3">
         <v>537400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>503600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>527400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>638400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>591300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>572400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>504200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>545000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>463500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>461800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>414900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>641700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>296000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>118800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>168000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>185000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>182800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>141300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>144600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>124000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>110000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>100300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>94400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>76600</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3">
         <v>18900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>18400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>165500</v>
+      </c>
+      <c r="E9" s="3">
         <v>153400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>156100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>137100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>120100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>133800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>125600</v>
+      </c>
+      <c r="K9" s="3">
+        <v>132300</v>
+      </c>
+      <c r="L9" s="3">
+        <v>165400</v>
+      </c>
+      <c r="M9" s="3">
+        <v>154900</v>
+      </c>
+      <c r="N9" s="3">
         <v>142100</v>
       </c>
-      <c r="H9" s="3">
-        <v>133800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>125600</v>
-      </c>
-      <c r="J9" s="3">
-        <v>132300</v>
-      </c>
-      <c r="K9" s="3">
-        <v>165400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>154900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>142100</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>125400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>124000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>125500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>135200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>130400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>58600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>39900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>40700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>29500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>16500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>13800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>12900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>477200</v>
+      </c>
+      <c r="E10" s="3">
         <v>483400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>447000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>417500</v>
       </c>
-      <c r="G10" s="3">
-        <v>422300</v>
-      </c>
       <c r="H10" s="3">
+        <v>394700</v>
+      </c>
+      <c r="I10" s="3">
         <v>403600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>378000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>395100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>473000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>436400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>430300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>361800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>419600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>339400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>336300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>279800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>511300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>190100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>121600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>145100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>142100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>91700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>111700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>120900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>103200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>91100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>84300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>76400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>61700</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="3">
         <v>5200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1415,8 +1434,8 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>575300</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -1427,21 +1446,21 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-6000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1451,21 +1470,21 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>2200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1475,8 +1494,8 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1511,95 +1530,98 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E15" s="3">
         <v>33100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>32700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>33500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>44600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>46000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>27400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="3">
         <v>3700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2500</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1609,8 +1631,8 @@
       <c r="AH15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>345200</v>
+      </c>
+      <c r="E17" s="3">
         <v>303500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>315200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>287100</v>
       </c>
-      <c r="G17" s="3">
-        <v>297400</v>
-      </c>
       <c r="H17" s="3">
+        <v>251400</v>
+      </c>
+      <c r="I17" s="3">
         <v>271700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>257100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>287600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>322700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>315700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>302300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>298400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>276800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>264600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>261400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>266200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>248200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>246300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>137800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>108700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>105800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>97300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>86800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>66800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>57700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>54800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>55900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>42000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>49000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>37000</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="3">
         <v>36000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>28600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E18" s="3">
         <v>333300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>287900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>267500</v>
       </c>
-      <c r="G18" s="3">
-        <v>267000</v>
-      </c>
       <c r="H18" s="3">
+        <v>263400</v>
+      </c>
+      <c r="I18" s="3">
         <v>265700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>246400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>239800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>315800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>275500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>270100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>205900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>268200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>198900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>148700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>393500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>49700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>79200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>85600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>43800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>74400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>86900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>69100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>54100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>58300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>45400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>39700</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,211 +1950,215 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E20" s="3">
         <v>80800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>78400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>90200</v>
       </c>
-      <c r="G20" s="3">
-        <v>96700</v>
-      </c>
       <c r="H20" s="3">
+        <v>97700</v>
+      </c>
+      <c r="I20" s="3">
         <v>88300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>85100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>109700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>127500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>140900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>148300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>114500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-218400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-124900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-259800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-173000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-522600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-308900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>146700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-10200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-14800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>14400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>10500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>251600</v>
+      </c>
+      <c r="E21" s="3">
         <v>285700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>244400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>209900</v>
       </c>
-      <c r="G21" s="3">
-        <v>199600</v>
-      </c>
       <c r="H21" s="3">
+        <v>195100</v>
+      </c>
+      <c r="I21" s="3">
         <v>210800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>191600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>162200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>221200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>179300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>167700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>133300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>88400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>111700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-106600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-216100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>146500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>66400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>82300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>84700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>56800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>77600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>59000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>45800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>51400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>37000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>28700</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2132,77 +2168,80 @@
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>6900</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E22" s="3">
         <v>102300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>82600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>67700</v>
       </c>
-      <c r="G22" s="3">
-        <v>51500</v>
-      </c>
       <c r="H22" s="3">
+        <v>51100</v>
+      </c>
+      <c r="I22" s="3">
         <v>51800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>45800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>36800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>28500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>33800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>34500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2212,18 +2251,18 @@
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
@@ -2248,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E23" s="3">
         <v>150300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>126900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>109500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-456500</v>
-      </c>
       <c r="H23" s="3">
+        <v>114700</v>
+      </c>
+      <c r="I23" s="3">
         <v>125600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>115500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>90000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>152100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>100800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>87600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>45500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-96900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-58100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-163600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-287600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>112800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>40700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>68900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>72700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>67000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>50600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>39200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>45800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>32000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>24200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>19900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E24" s="3">
         <v>24900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20300</v>
       </c>
-      <c r="G24" s="3">
-        <v>15900</v>
-      </c>
       <c r="H24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I24" s="3">
         <v>23300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-33700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>23900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>15300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>5200</v>
       </c>
       <c r="AH24" s="3">
         <v>5200</v>
       </c>
       <c r="AI24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E26" s="3">
         <v>125400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>107800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>89200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-472400</v>
-      </c>
       <c r="H26" s="3">
+        <v>99400</v>
+      </c>
+      <c r="I26" s="3">
         <v>102200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>89900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>69700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>135200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>82400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-98100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-62700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-161800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-253800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>101900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>57300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>48800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>31300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>48800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>32200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>16700</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E27" s="3">
         <v>132600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>109400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>90100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-472800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>99100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>89300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>74500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>134200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>81800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>63300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-97700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-62800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-160400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-252100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>102500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>58700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>49900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>31300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>48600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>32300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>16400</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,35 +2965,38 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E29" s="3">
         <v>8800</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>2400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>900</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>-572000</v>
+      </c>
+      <c r="I29" s="3">
         <v>-2700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>4800</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-80800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-78400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-90200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-96700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-97700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-88300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-85100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-109700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-127500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-140900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-148300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-114500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>218400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>124900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>259800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>173000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>522600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>308900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-146700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>10200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>12900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>29500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>19600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>14800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>12500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>13400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15400</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E33" s="3">
         <v>132600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>109400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>90100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-472800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>99100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>89300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>74500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>134200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>81800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>63300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-97700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-62800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-160400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-252100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>102500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>58700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>49900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>31300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>48600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>33100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>16400</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E35" s="3">
         <v>132600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>109400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>90100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-472800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>99100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>89300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>74500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>134200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>81800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>63300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-97700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-62800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-160400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-252100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>102500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>58700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>49900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>31300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>48600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>33100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>16400</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,104 +3958,105 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>875400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1042200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>951700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>985500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>845200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>737000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>854400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>994600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>448500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>739500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>456800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>366500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>271900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>432900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>759000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>835700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>907400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>612600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1137100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>360800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>457800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>429000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>543400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>299300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>178900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>45300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>53200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>33400</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3983,104 +4069,107 @@
       <c r="AL41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>203200</v>
+      </c>
+      <c r="E42" s="3">
         <v>65500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>71100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>717500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>409000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>724500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>643300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1332600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1069800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>498700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>505900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>402300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>452300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>968100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1679500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1520700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1601800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>154300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>474300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>542500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>522600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>507400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>497800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>494300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>26300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>48800</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4093,104 +4182,107 @@
       <c r="AL42" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7924900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7556200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6872500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6296100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4938900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5008400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5117400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5449000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5067800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4326600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3935400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3823300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3833700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3594600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3681400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3862800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4115000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3562700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3331500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3326300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3393000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2683200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2593100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2653500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2338800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2375200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1971100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4203,8 +4295,11 @@
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4241,8 +4336,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4313,104 +4408,107 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1244700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1266500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1248400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>528500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1563900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1527600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1366600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1426800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1422900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>993200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>952300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>881200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>75900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>659900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>591100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>619300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>443700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>248600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>206600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>172200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>123600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>82800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>51100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>28000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4423,104 +4521,107 @@
       <c r="AL45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10248200</v>
+      </c>
+      <c r="E46" s="3">
         <v>9930400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9118000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7835600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7431800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7344100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7357600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7962900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7656700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6492300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6095400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5740600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5510400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5173200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5598900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5795500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6044000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5508700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5916500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5578400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5477000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5547500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3463800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3417800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3399400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2934700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2921800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2492300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4533,104 +4634,107 @@
       <c r="AL46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E47" s="3">
         <v>20700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>76600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>91100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>75400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>209000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>276400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>435900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>694500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>81200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>82600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>9700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4643,104 +4747,107 @@
       <c r="AL47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>318100</v>
+      </c>
+      <c r="E48" s="3">
         <v>333300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>341700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>335700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>304800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>327200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>315700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>344300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>348900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>338200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>360400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>356600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>295000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>303500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>336800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>329100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>316800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>262100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>188200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>172800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>134200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>126500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>117700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>117200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>101300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>88500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>70500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>62800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>47500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>46800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>57400</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4753,104 +4860,107 @@
       <c r="AL48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>355900</v>
+      </c>
+      <c r="E49" s="3">
         <v>360300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>343900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>948300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>874300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1640200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1599600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1747200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1806100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1742000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1796000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1700900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1551500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1588700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1721100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1692800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1673300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1655300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>220700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>205200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>194600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>151500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>135900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>75200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>69000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>67800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>60700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>58500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>54900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>56800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>55900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4863,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,104 +5199,107 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E52" s="3">
         <v>32900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>34200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>159300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>183800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>186900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>161700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>189000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>135800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>109100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>95100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>51500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>50200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>46400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>49600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>43900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>46600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>51200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>51900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>48400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>46800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>54500</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5193,8 +5312,11 @@
       <c r="AL52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,104 +5425,107 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11310300</v>
+      </c>
+      <c r="E54" s="3">
         <v>10995000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10122500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9406800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8862500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9536000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9492700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10290600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10035200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8777000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8451500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8000700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7592800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7340400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7919100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8188100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8496900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7997900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7129000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6132700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5939900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5888100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3769200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3669500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3621200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3143000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3109300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2667700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5413,8 +5538,11 @@
       <c r="AL54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,104 +5622,105 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E57" s="3">
         <v>126100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>125700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>125900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>103600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>94700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>105900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>90100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>87800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>98100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3086800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2812000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>79300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3075300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3248800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2991400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2156500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1673900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1749800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1691700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1382700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1118700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1218600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1073100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1105200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1088800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>912300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>865300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>940200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5603,104 +5733,107 @@
       <c r="AL57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1569300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1491900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>978800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>861400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>803500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>517300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>547200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>444900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>387400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>394300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>396000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>381200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>507300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>462000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>681200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>889600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>781800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>572100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>672500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>656700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>588400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>570000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>739900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>839400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>930600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>512800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>398400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>246700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>138700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3900</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5713,104 +5846,107 @@
       <c r="AL58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5643500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5249000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4996300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4575900</v>
       </c>
-      <c r="G59" s="3">
-        <v>4398600</v>
-      </c>
       <c r="H59" s="3">
+        <v>4396200</v>
+      </c>
+      <c r="I59" s="3">
         <v>4423800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4679800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5212600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5324400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4516500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4211500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3994000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>930400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>803600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>740000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>701100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>569300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>422000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>210700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>171300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>125200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>86200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>57700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>43600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>34700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>29100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>46900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>27900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5823,104 +5959,107 @@
       <c r="AL59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7480800</v>
+      </c>
+      <c r="E60" s="3">
         <v>6964800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6181600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5637000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5421900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5155500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5412500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5838400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5941700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5111600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4792300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4552000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4524500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4077700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1500500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4666000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4599900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3985500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3039800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2502000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2503300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2386800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2208700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2015800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2192900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1619400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1539300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1370300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>923000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>972100</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
@@ -5933,104 +6072,107 @@
       <c r="AL60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1622800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1647100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1654100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1481900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1281500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1331200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1122000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1207200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>750000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>546500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>524200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>525300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>490400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>638000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>680400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>630100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>906000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>860300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1044200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>560400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>549800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>582500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>241400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>397800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>315400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>462600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>531100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>295800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>367400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>381000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>481100</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
@@ -6043,104 +6185,107 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E62" s="3">
         <v>116600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>101100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>150700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>136700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>123900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>106300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>141800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>206200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>180400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>177800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>179000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>250300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>266800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3201800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>209800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>240400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>227700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>111300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>89400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>81800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>61100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>51000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>20200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>18300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>18800</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6153,8 +6298,11 @@
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,104 +6637,107 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9306800</v>
+      </c>
+      <c r="E66" s="3">
         <v>8782700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7990100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7406800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6950200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6720900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6751400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7298900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7010600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5939900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5599000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5356300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5275400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4997100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5399800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5528800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5764700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5090800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4210900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3163600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3160900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3048700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2519400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2442000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2518100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2102100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2090000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1681600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6593,8 +6750,11 @@
       <c r="AL66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,104 +7243,107 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>358300</v>
+      </c>
+      <c r="E72" s="3">
         <v>276500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>140700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>473400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>367100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>307400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>240900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>103600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-38800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2407600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2430900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2614100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2732500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2954400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3096800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3211200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2986400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2794100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2861600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1274000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1250900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1116500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1055200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1034600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>998300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>918700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>132900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>175600</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7183,8 +7356,11 @@
       <c r="AL72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,104 +7695,107 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1996200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2204300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2122800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1991200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1904000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2805200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2731400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2981100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3013500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2826000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2840900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2633400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2317400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2343300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2519300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2659300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2732200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2907100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2918100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2969000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2778900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2839400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1249900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1227500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1103100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1040900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1019300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>986200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>908600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>126900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>167300</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7623,8 +7808,11 @@
       <c r="AL76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E81" s="3">
         <v>132600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>109400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>90100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-472800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>99100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>89300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>74500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>134200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>81800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>63300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-97700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-62800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-160400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-252100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>102500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>58700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>49900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>31300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>48600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>33100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>16400</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E83" s="3">
         <v>32200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>39500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>43100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>16400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL83" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-196200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>71100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>108900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-48600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-129000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-493100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-85900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>172700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>230700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>61700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>143200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>159400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>120100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>358300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>256000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>45400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-326800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>219400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>71400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-122500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-353300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-55200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>15400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL89" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-69100</v>
-      </c>
       <c r="H91" s="3">
+        <v>70600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-31200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-50100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-67200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-155300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-109300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-216800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-241800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-546400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-151300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-64800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-17800</v>
       </c>
       <c r="Z91" s="3">
         <v>-17800</v>
       </c>
       <c r="AA91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-36400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL91" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-191800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-73200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-104100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>538400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-351500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>263600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-105400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>10200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-149700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-51100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-150500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-596400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>167200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-121200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>282300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>97400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>16900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>4300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>26700</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL94" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9326,8 +9559,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-73700</v>
+      </c>
+      <c r="E100" s="3">
         <v>309200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-46800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>322800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>93300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>515300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>126100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>22200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-175200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-63100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-183300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-222700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-71400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>225100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-328900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>345300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>29800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1704200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-255100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>279100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>35200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>387000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>870200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>229100</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3600</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>2000</v>
       </c>
       <c r="K101" s="3">
         <v>2000</v>
       </c>
       <c r="L101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-500</v>
       </c>
       <c r="Z101" s="3">
         <v>-500</v>
       </c>
       <c r="AA101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL101" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM101" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-135300</v>
+      </c>
+      <c r="E102" s="3">
         <v>39700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>73700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>196300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-134100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>560600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-312600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>298400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>67700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-149300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-266700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-76700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-65300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>293400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-570100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>776300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-113000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>47600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-114400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>246200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>108400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>133600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>15600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-39500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>125900</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>STNE</t>
   </si>
@@ -656,505 +656,518 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>635500</v>
+      </c>
+      <c r="E8" s="3">
         <v>642600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>636900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>603100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>554600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>514800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>537400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>503600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>527400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>638400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>591300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>572400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>504200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>545000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>463500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>461800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>414900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>641700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>296000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>118800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>168000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>185000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>182800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>130600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>141300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>144600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>124000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>110000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>100300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>94400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>76600</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>18900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>18400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E9" s="3">
         <v>165500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>153400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>156100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>137100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>120100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>133800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>125600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>132300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>165400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>154900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>142400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>125400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>124000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>125500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>135200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>130400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>105900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>58600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>40700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>29500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>16400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>18800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>13800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>12900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E10" s="3">
         <v>477200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>483400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>447000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>417500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>394700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>403600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>378000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>395100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>473000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>436400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>430300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>361800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>419600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>339400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>336300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>279800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>511300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>190100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>60200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>121600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>145100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>142100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>91700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>111700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>120900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>103200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>91100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>84300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>76400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>61700</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3">
         <v>5200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1207,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1307,8 +1321,11 @@
       <c r="AM12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1437,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1449,21 +1469,21 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>-6000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1473,21 +1493,21 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1497,8 +1517,8 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1533,8 +1553,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,89 +1565,89 @@
         <v>32100</v>
       </c>
       <c r="E15" s="3">
+        <v>32100</v>
+      </c>
+      <c r="F15" s="3">
         <v>33100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>44600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>46000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>27400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4000</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>3700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2500</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1634,8 +1657,8 @@
       <c r="AI15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1710,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>353800</v>
+      </c>
+      <c r="E17" s="3">
         <v>345200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>303500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>315200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>287100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>251400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>271700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>257100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>287600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>322700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>315700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>302300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>298400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>276800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>264600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>261400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>266200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>248200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>246300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>137800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>108700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>105800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>97300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>86800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>66800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>57700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>54800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>55900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>42000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>49000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>37000</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="3">
         <v>36000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>28600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>281700</v>
+      </c>
+      <c r="E18" s="3">
         <v>297500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>333300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>287900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>267500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>263400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>265700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>246400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>239800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>315800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>275500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>270100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>205900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>268200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>198900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>148700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>393500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>49700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-19000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>59300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>79200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>85600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>43800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>74400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>86900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>69100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>54100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>58300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>45400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>39700</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-10200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,217 +1984,221 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E20" s="3">
         <v>78000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>80800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>78400</v>
       </c>
-      <c r="G20" s="3">
-        <v>90200</v>
-      </c>
       <c r="H20" s="3">
+        <v>82200</v>
+      </c>
+      <c r="I20" s="3">
         <v>97700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>88300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>85100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>109700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>127500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>140900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>148300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>114500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-218400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-124900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-259800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-173000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-522600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-308900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>146700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-14800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>14400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>10500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E21" s="3">
         <v>251600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>285700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>244400</v>
       </c>
-      <c r="G21" s="3">
-        <v>209900</v>
-      </c>
       <c r="H21" s="3">
+        <v>218000</v>
+      </c>
+      <c r="I21" s="3">
         <v>195100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>210800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>191600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>162200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>221200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>179300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>167700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>133300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>88400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>111700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-19900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-106600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-216100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>146500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>66400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>82300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>84700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>43600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>56800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>77600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>59000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>45800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>51400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>28700</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2171,80 +2208,83 @@
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="3">
         <v>6900</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E22" s="3">
         <v>97900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>102300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>82600</v>
       </c>
-      <c r="G22" s="3">
-        <v>67700</v>
-      </c>
       <c r="H22" s="3">
+        <v>75700</v>
+      </c>
+      <c r="I22" s="3">
         <v>51100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>51800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>45800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>40100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>36200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>36800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>28500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>37500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>34500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>28400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2254,18 +2294,18 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
@@ -2290,234 +2330,243 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E23" s="3">
         <v>121600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>150300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>126900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>109500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>114700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>125600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>115500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>90000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>152100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>100800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>87600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>60600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>45500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-96900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-58100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-163600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-287600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>112800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>68900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>72700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>44900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>67000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>50600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>39200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>45800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>32000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>24200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>19900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-221100</v>
+      </c>
+      <c r="E24" s="3">
         <v>10800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-33700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>23900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7500</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>5200</v>
       </c>
       <c r="AI24" s="3">
         <v>5200</v>
       </c>
       <c r="AJ24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>341300</v>
+      </c>
+      <c r="E26" s="3">
         <v>110800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>125400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>107800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>89200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>99400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>102200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>89900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>69700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-98100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-62700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-161800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-253800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>101900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>57300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>48800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>24200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>31300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>48800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>35300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>32200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>16700</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-19400</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E27" s="3">
         <v>90800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>132600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>109400</v>
       </c>
-      <c r="G27" s="3">
-        <v>90100</v>
-      </c>
       <c r="H27" s="3">
+        <v>89700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-472800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>99100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>89300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>74500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>134200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>81800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-97700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-62800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-160400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-252100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>102500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>58700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>49900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>24800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>31300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>48600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>35300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>32300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>33100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>16400</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,38 +3026,41 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-19200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>8800</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>2400</v>
       </c>
-      <c r="G29" s="3">
-        <v>900</v>
-      </c>
       <c r="H29" s="3">
+        <v>600</v>
+      </c>
+      <c r="I29" s="3">
         <v>-572000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>4800</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,234 +3374,243 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-78000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-80800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-78400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-90200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-97700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-88300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-85100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-109700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-127500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-140900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-148300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-114500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>218400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>124900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>259800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>173000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>522600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>308900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-146700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>29500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>19600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>18200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>14800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>12500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>13400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15400</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-14400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E33" s="3">
         <v>90800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>132600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>109400</v>
       </c>
-      <c r="G33" s="3">
-        <v>90100</v>
-      </c>
       <c r="H33" s="3">
+        <v>89700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-472800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>99100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>89300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>74500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>134200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>81800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>63300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-97700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-62800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-160400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-252100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>102500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>58700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>49900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>24800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>48600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>35300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>32300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>33100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>16400</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E35" s="3">
         <v>90800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>132600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>109400</v>
       </c>
-      <c r="G35" s="3">
-        <v>90100</v>
-      </c>
       <c r="H35" s="3">
+        <v>89700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-472800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>99100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>89300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>74500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>134200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>81800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>63300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-97700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-62800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-160400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-252100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>102500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>58700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>49900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>24800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>48600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>35300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>32300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>33100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>16400</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,107 +4045,108 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1167800</v>
+      </c>
+      <c r="E41" s="3">
         <v>875400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1042200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>951700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>985500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>845200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>737000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>854400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>994600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>448500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>739500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>456800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>366500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>271900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>432900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>759000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>835700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>907400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>612600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1137100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>360800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>457800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>429000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>543400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>299300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>178900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>45300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>30100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>53200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>32100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33400</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
@@ -4072,107 +4159,110 @@
       <c r="AM41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>792500</v>
+      </c>
+      <c r="E42" s="3">
         <v>203200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>65500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>45400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>83700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>71100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>717500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>409000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>724500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>643300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1332600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1069800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>498700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>505900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>402300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>452300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>968100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1679500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1520700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1601800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>154300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>474300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>542500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>522600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>507400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>497800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>494300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>26300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>48800</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4185,107 +4275,110 @@
       <c r="AM42" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN42" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7736300</v>
+      </c>
+      <c r="E43" s="3">
         <v>7924900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7556200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6872500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6296100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4938900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5008400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5117400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5449000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5067800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4326600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3935400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3823300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3833700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3594600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3681400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3862800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4115000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3562700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3331500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3326300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3393000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2683200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2593100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2653500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2338800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2375200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1971100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1667400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1233300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1385400</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4298,8 +4391,11 @@
       <c r="AM43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4339,8 +4435,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4411,107 +4507,110 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>344200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1244700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1266500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1248400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>528500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1563900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1527600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1366600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1426800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1422900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>993200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>952300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>881200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>72200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>75900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>659900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>591100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>619300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>443700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>248600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>206600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>172200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>123600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>82800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>51100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4000</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4524,107 +4623,110 @@
       <c r="AM45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10040800</v>
+      </c>
+      <c r="E46" s="3">
         <v>10248200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9930400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7835600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7431800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7344100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7357600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7962900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7656700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6492300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6095400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5740600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5510400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5173200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5598900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5795500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6044000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5508700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5916500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5578400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5477000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5547500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3463800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3417800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3399400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2934700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2921800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2492300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2218900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1300000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1471500</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4637,107 +4739,110 @@
       <c r="AM46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E47" s="3">
         <v>17500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>76600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>91100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>75400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>209000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>276400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>435900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>694500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>81200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>82600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4000</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4750,107 +4855,110 @@
       <c r="AM47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E48" s="3">
         <v>318100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>333300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>341700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>335700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>304800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>327200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>315700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>344300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>348900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>338200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>360400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>356600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>295000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>303500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>336800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>329100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>316800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>262100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>188200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>172800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>134200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>126500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>117700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>117200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>101300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>88500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>62800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>47500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>46800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>57400</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4863,107 +4971,110 @@
       <c r="AM48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E49" s="3">
         <v>355900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>360300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>343900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>948300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>874300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1640200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1599600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1747200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1806100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1742000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1796000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1700900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1551500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1588700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1721100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1692800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1673300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1655300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>220700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>205200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>194600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>151500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>135900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>75200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>67800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>60700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>58500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>54900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>56800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>55900</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4976,8 +5087,11 @@
       <c r="AM49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,107 +5319,110 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E52" s="3">
         <v>32300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>34200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>159300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>183800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>186900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>161700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>189000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>135800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>109100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>95100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>51500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>50200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>46400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>49600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>43900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>46600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>51200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>51900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>48400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>46800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>54500</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5315,8 +5435,11 @@
       <c r="AM52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,107 +5551,110 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11476200</v>
+      </c>
+      <c r="E54" s="3">
         <v>11310300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10995000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10122500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9406800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8862500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9536000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9492700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10290600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10035200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8777000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8451500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8000700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7592800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7340400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7919100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8188100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8496900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7997900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7129000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6132700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5939900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5888100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3769200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3669500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3621200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3143000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3109300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2667700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2371500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1452700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1643300</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5541,8 +5667,11 @@
       <c r="AM54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,107 +5753,108 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E57" s="3">
         <v>154000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>126100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>125700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>125900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>105900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>90100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>87800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3086800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2812000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>79300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3075300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3248800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2991400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2156500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1673900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1749800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1691700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1382700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1118700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1218600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1073100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1105200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1088800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>912300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>865300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>940200</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5736,107 +5867,110 @@
       <c r="AM57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1755400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1569300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1491900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>978800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>861400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>803500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>517300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>547200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>444900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>387400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>394300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>396000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>381200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>507300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>462000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>681200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>889600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>781800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>572100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>672500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>656700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>588400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>570000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>739900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>839400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>930600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>512800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>398400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>246700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>138700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3900</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5849,107 +5983,110 @@
       <c r="AM58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5539600</v>
+      </c>
+      <c r="E59" s="3">
         <v>5643500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5249000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4996300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4575900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4396200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4423800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4679800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5212600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5324400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4516500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4211500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3994000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>930400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>803600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>740000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>701100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>569300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>422000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>210700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>171300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>165100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>125200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>86200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>57700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>43600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>33500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>34700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>29100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>46900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>27900</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5962,107 +6099,110 @@
       <c r="AM59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7522300</v>
+      </c>
+      <c r="E60" s="3">
         <v>7480800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6964800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6181600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5637000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5421900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5155500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5412500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5838400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5941700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5111600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4792300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4552000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4524500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4077700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1500500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4666000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4599900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3985500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3039800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2502000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2503300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2386800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2208700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2015800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2192900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1619400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1539300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1370300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1080200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>923000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>972100</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>4</v>
       </c>
@@ -6075,107 +6215,110 @@
       <c r="AM60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1391100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1622800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1647100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1654100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1481900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1281500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1331200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1122000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1207200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>750000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>546500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>524200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>525300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>490400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>638000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>680400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>630100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>906000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>860300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1044200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>560400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>549800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>582500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>241400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>397800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>315400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>462600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>531100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>295800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>367400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>381000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>481100</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
@@ -6188,107 +6331,110 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E62" s="3">
         <v>147200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>116600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>101100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>150700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>136700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>123900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>106300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>141800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>206200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>180400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>177800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>179000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>250300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>266800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3201800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>209800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>240400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>227700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>111300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>89400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>81800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>61100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>51000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>20200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>19700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>15400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>18300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>18800</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6301,8 +6447,11 @@
       <c r="AM62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,107 +6795,110 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9121700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9306800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8782700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7990100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7406800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6950200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6720900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6751400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7298900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7010600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5939900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5599000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5356300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5275400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4997100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5399800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5528800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5764700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5090800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4210900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3163600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3160900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3048700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2519400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2442000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2518100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2102100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2090000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1681600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1462900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1325800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1476000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6753,8 +6911,11 @@
       <c r="AM66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,107 +7417,110 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>705400</v>
+      </c>
+      <c r="E72" s="3">
         <v>358300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>276500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>140700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-56000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>473400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>367100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>307400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>240900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>103600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-38800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2407600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2430900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2614100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2732500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2954400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3096800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3211200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2986400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2794100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2861600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1274000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1250900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1116500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1055200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1034600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>998300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>918700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>132900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>175600</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7359,8 +7533,11 @@
       <c r="AM72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,107 +7881,110 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2346700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1996200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2204300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2122800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1991200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1904000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2805200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2731400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2981100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3013500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2826000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2840900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2633400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2317400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2343300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2519300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2659300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2732200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2907100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2918100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2969000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2778900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2839400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1249900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1227500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1103100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1040900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1019300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>986200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>908600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>126900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>167300</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7811,8 +7997,11 @@
       <c r="AM76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E81" s="3">
         <v>90800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>132600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>109400</v>
       </c>
-      <c r="G81" s="3">
-        <v>90100</v>
-      </c>
       <c r="H81" s="3">
+        <v>89700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-472800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>99100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>89300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>74500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>134200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>81800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>63300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-97700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-62800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-160400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-252100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>102500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>58700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>49900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>24800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>48600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>35300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>32300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>33100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>16400</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,121 +8394,125 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E83" s="3">
         <v>28800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>38600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>39500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>43100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>16400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4400</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM83" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN83" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>640900</v>
+      </c>
+      <c r="E89" s="3">
         <v>128900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-196200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>108900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-48600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-129000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-493100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-85900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>172700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>230700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>61700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>143200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>159400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>120100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>358300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>256000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>45400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-326800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>219400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>71400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-122500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-353300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-55200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-379200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-32200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-54900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-130100</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM89" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,121 +9248,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E91" s="3">
         <v>77400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>70600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-40700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-67200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-155300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-109300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-216800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-241800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-546400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-151300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-64800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-17800</v>
       </c>
       <c r="AA91" s="3">
         <v>-17800</v>
       </c>
       <c r="AB91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-36400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM91" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN91" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9594,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-191800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-72100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-73200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>538400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-351500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>263600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-105400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-149700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-150500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-596400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>167200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-121200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1492000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>282300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>97400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>16900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-470400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>4300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>26700</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM94" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN94" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9562,8 +9796,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9634,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,343 +10216,355 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-407600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-73700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>309200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-46800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>322800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>93300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>515300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>126100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-175200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-63100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-183300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-222700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-71400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>225100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-328900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>345300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1704200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-255100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>279100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>35200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>387000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>870200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>229100</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3600</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>2000</v>
       </c>
       <c r="L101" s="3">
         <v>2000</v>
       </c>
       <c r="M101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-500</v>
       </c>
       <c r="AA101" s="3">
         <v>-500</v>
       </c>
       <c r="AB101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>200</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM101" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN101" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>199300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-135300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>73700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>196300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-134100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-44100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>560600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-312600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>298400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>72000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>67700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-149300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-266700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-76700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-65300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>293400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-570100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>776300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-113000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>47600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-114400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>246200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>108400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>133600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>15600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-39500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>22200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>125900</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
